--- a/artfynd/A 59973-2025 artfynd.xlsx
+++ b/artfynd/A 59973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134095278</v>
       </c>
       <c r="B2" t="n">
-        <v>79347</v>
+        <v>79348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>134095276</v>
       </c>
       <c r="B3" t="n">
-        <v>79379</v>
+        <v>79380</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>134095306</v>
       </c>
       <c r="B4" t="n">
-        <v>57964</v>
+        <v>57965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>134095299</v>
       </c>
       <c r="B5" t="n">
-        <v>80412</v>
+        <v>80413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,32 +1116,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134095305</v>
+        <v>134095313</v>
       </c>
       <c r="B6" t="n">
-        <v>80412</v>
+        <v>79380</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589501</v>
+        <v>589577</v>
       </c>
       <c r="R6" t="n">
-        <v>6914218</v>
+        <v>6914208</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134095285</v>
+        <v>134095248</v>
       </c>
       <c r="B7" t="n">
-        <v>79379</v>
+        <v>79380</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589377</v>
+        <v>589533</v>
       </c>
       <c r="R7" t="n">
-        <v>6914229</v>
+        <v>6914053</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,32 +1330,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134095313</v>
+        <v>134095305</v>
       </c>
       <c r="B8" t="n">
-        <v>79379</v>
+        <v>80413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589577</v>
+        <v>589501</v>
       </c>
       <c r="R8" t="n">
-        <v>6914208</v>
+        <v>6914218</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134095248</v>
+        <v>134095285</v>
       </c>
       <c r="B9" t="n">
-        <v>79379</v>
+        <v>79380</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589533</v>
+        <v>589377</v>
       </c>
       <c r="R9" t="n">
-        <v>6914053</v>
+        <v>6914229</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,7 +1547,7 @@
         <v>134095260</v>
       </c>
       <c r="B10" t="n">
-        <v>79347</v>
+        <v>79348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,32 +1651,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134095289</v>
+        <v>134095293</v>
       </c>
       <c r="B11" t="n">
-        <v>79347</v>
+        <v>80413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589423</v>
+        <v>589461</v>
       </c>
       <c r="R11" t="n">
-        <v>6914227</v>
+        <v>6914225</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134095328</v>
+        <v>134095289</v>
       </c>
       <c r="B12" t="n">
-        <v>57964</v>
+        <v>79348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,42 +1769,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589682</v>
+        <v>589423</v>
       </c>
       <c r="R12" t="n">
-        <v>6914127</v>
+        <v>6914227</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1836,7 +1828,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1846,19 +1838,14 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påbörjade bohål i grantickerötad granhögstubbe. Hålen sitter 1.5 meter respektive 2.5 m ovan mark.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -1878,32 +1865,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134095270</v>
+        <v>134095291</v>
       </c>
       <c r="B13" t="n">
-        <v>91907</v>
+        <v>91947</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589483</v>
+        <v>589424</v>
       </c>
       <c r="R13" t="n">
-        <v>6914142</v>
+        <v>6914230</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1948,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1945,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,32 +1972,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134095346</v>
+        <v>134095270</v>
       </c>
       <c r="B14" t="n">
-        <v>79379</v>
+        <v>91910</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2020,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589671</v>
+        <v>589483</v>
       </c>
       <c r="R14" t="n">
-        <v>6914046</v>
+        <v>6914142</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2055,7 +2042,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2052,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,32 +2079,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134095293</v>
+        <v>134095346</v>
       </c>
       <c r="B15" t="n">
-        <v>80412</v>
+        <v>79380</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589461</v>
+        <v>589671</v>
       </c>
       <c r="R15" t="n">
-        <v>6914225</v>
+        <v>6914046</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2162,7 +2149,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2159,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,32 +2186,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134095291</v>
+        <v>134095309</v>
       </c>
       <c r="B16" t="n">
-        <v>91944</v>
+        <v>80413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2234,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589424</v>
+        <v>589523</v>
       </c>
       <c r="R16" t="n">
-        <v>6914230</v>
+        <v>6914208</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2269,7 +2256,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2279,7 +2266,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134095252</v>
+        <v>134095337</v>
       </c>
       <c r="B17" t="n">
-        <v>79379</v>
+        <v>91947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2317,21 +2304,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589531</v>
+        <v>589774</v>
       </c>
       <c r="R17" t="n">
-        <v>6914096</v>
+        <v>6914028</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2376,7 +2363,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2386,7 +2373,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2413,32 +2400,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134095281</v>
+        <v>134095261</v>
       </c>
       <c r="B18" t="n">
-        <v>92376</v>
+        <v>79380</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2448,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589375</v>
+        <v>589508</v>
       </c>
       <c r="R18" t="n">
-        <v>6914203</v>
+        <v>6914122</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2483,7 +2470,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2493,7 +2480,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2520,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134095337</v>
+        <v>134095324</v>
       </c>
       <c r="B19" t="n">
-        <v>91944</v>
+        <v>79380</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2531,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2555,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589774</v>
+        <v>589658</v>
       </c>
       <c r="R19" t="n">
-        <v>6914028</v>
+        <v>6914166</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2590,7 +2577,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2600,7 +2587,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2627,10 +2614,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134095265</v>
+        <v>134095252</v>
       </c>
       <c r="B20" t="n">
-        <v>57964</v>
+        <v>79380</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2638,42 +2625,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589546</v>
+        <v>589531</v>
       </c>
       <c r="R20" t="n">
-        <v>6914177</v>
+        <v>6914096</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2705,7 +2684,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,12 +2694,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2747,32 +2721,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134095324</v>
+        <v>134095281</v>
       </c>
       <c r="B21" t="n">
-        <v>79379</v>
+        <v>92379</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2782,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589658</v>
+        <v>589375</v>
       </c>
       <c r="R21" t="n">
-        <v>6914166</v>
+        <v>6914203</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2817,7 +2791,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2827,7 +2801,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2854,10 +2828,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134095261</v>
+        <v>134095265</v>
       </c>
       <c r="B22" t="n">
-        <v>79379</v>
+        <v>57965</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,34 +2839,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589508</v>
+        <v>589546</v>
       </c>
       <c r="R22" t="n">
-        <v>6914122</v>
+        <v>6914177</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2924,7 +2906,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2934,7 +2916,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2961,32 +2948,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134095309</v>
+        <v>134095350</v>
       </c>
       <c r="B23" t="n">
-        <v>80412</v>
+        <v>79380</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2996,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589523</v>
+        <v>589620</v>
       </c>
       <c r="R23" t="n">
-        <v>6914208</v>
+        <v>6914079</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3031,7 +3018,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3041,7 +3028,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3068,10 +3055,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134095350</v>
+        <v>134095335</v>
       </c>
       <c r="B24" t="n">
-        <v>79379</v>
+        <v>79380</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589620</v>
+        <v>589737</v>
       </c>
       <c r="R24" t="n">
-        <v>6914079</v>
+        <v>6914072</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3138,7 +3125,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3148,7 +3135,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3175,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134095335</v>
+        <v>134095254</v>
       </c>
       <c r="B25" t="n">
-        <v>79379</v>
+        <v>79380</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589737</v>
+        <v>589525</v>
       </c>
       <c r="R25" t="n">
-        <v>6914072</v>
+        <v>6914090</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3245,7 +3232,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3255,7 +3242,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3282,10 +3269,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134095336</v>
+        <v>134095292</v>
       </c>
       <c r="B26" t="n">
-        <v>91944</v>
+        <v>80453</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3293,21 +3280,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3317,10 +3304,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589761</v>
+        <v>589461</v>
       </c>
       <c r="R26" t="n">
-        <v>6914026</v>
+        <v>6914224</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3352,7 +3339,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3362,7 +3349,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3392,7 +3379,7 @@
         <v>134095294</v>
       </c>
       <c r="B27" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3496,10 +3483,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134095292</v>
+        <v>134095279</v>
       </c>
       <c r="B28" t="n">
-        <v>80452</v>
+        <v>91947</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,21 +3494,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3531,10 +3518,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589461</v>
+        <v>589373</v>
       </c>
       <c r="R28" t="n">
-        <v>6914224</v>
+        <v>6914203</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3566,7 +3553,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3576,7 +3563,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,45 +3590,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134095323</v>
+        <v>134095359</v>
       </c>
       <c r="B29" t="n">
-        <v>79347</v>
+        <v>57152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589690</v>
+        <v>589567</v>
       </c>
       <c r="R29" t="n">
-        <v>6914184</v>
+        <v>6914071</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3673,7 +3668,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3683,7 +3678,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3710,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134095254</v>
+        <v>134095336</v>
       </c>
       <c r="B30" t="n">
-        <v>79379</v>
+        <v>91947</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3721,21 +3716,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3740,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589525</v>
+        <v>589761</v>
       </c>
       <c r="R30" t="n">
-        <v>6914090</v>
+        <v>6914026</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3780,7 +3775,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3790,7 +3785,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3817,53 +3812,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134095359</v>
+        <v>134095323</v>
       </c>
       <c r="B31" t="n">
-        <v>57151</v>
+        <v>79348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589567</v>
+        <v>589690</v>
       </c>
       <c r="R31" t="n">
-        <v>6914071</v>
+        <v>6914184</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3895,7 +3882,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3905,7 +3892,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3932,10 +3919,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134095279</v>
+        <v>134095287</v>
       </c>
       <c r="B32" t="n">
-        <v>91944</v>
+        <v>80453</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3943,21 +3930,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3967,10 +3954,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589373</v>
+        <v>589437</v>
       </c>
       <c r="R32" t="n">
-        <v>6914203</v>
+        <v>6914217</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4002,7 +3989,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4012,7 +3999,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4039,10 +4026,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134095303</v>
+        <v>134095249</v>
       </c>
       <c r="B33" t="n">
-        <v>89326</v>
+        <v>79348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4050,21 +4037,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4074,13 +4061,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589501</v>
+        <v>589521</v>
       </c>
       <c r="R33" t="n">
-        <v>6914225</v>
+        <v>6914058</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4109,7 +4096,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4119,7 +4106,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,10 +4133,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134095287</v>
+        <v>134095303</v>
       </c>
       <c r="B34" t="n">
-        <v>80452</v>
+        <v>89328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4157,21 +4144,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4181,13 +4168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589437</v>
+        <v>589501</v>
       </c>
       <c r="R34" t="n">
-        <v>6914217</v>
+        <v>6914225</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4216,7 +4203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4226,7 +4213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4253,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134095249</v>
+        <v>134095330</v>
       </c>
       <c r="B35" t="n">
-        <v>79347</v>
+        <v>83333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4264,21 +4251,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4288,10 +4275,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589521</v>
+        <v>589701</v>
       </c>
       <c r="R35" t="n">
-        <v>6914058</v>
+        <v>6914115</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4323,7 +4310,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4333,7 +4320,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,10 +4347,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134095330</v>
+        <v>134095258</v>
       </c>
       <c r="B36" t="n">
-        <v>83332</v>
+        <v>91947</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4371,21 +4358,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4395,10 +4382,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589701</v>
+        <v>589495</v>
       </c>
       <c r="R36" t="n">
-        <v>6914115</v>
+        <v>6914097</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4430,7 +4417,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4440,7 +4427,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4467,10 +4454,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134095258</v>
+        <v>134095349</v>
       </c>
       <c r="B37" t="n">
-        <v>91944</v>
+        <v>57965</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4478,34 +4465,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589495</v>
+        <v>589619</v>
       </c>
       <c r="R37" t="n">
-        <v>6914097</v>
+        <v>6914055</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4537,7 +4532,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4547,7 +4542,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4574,10 +4574,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134095349</v>
+        <v>134095348</v>
       </c>
       <c r="B38" t="n">
-        <v>57964</v>
+        <v>57965</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589619</v>
+        <v>589625</v>
       </c>
       <c r="R38" t="n">
-        <v>6914055</v>
+        <v>6914048</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4697,7 +4697,7 @@
         <v>134095320</v>
       </c>
       <c r="B39" t="n">
-        <v>80480</v>
+        <v>80481</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134095348</v>
+        <v>134095341</v>
       </c>
       <c r="B40" t="n">
-        <v>57964</v>
+        <v>79348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4812,42 +4812,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589625</v>
+        <v>589783</v>
       </c>
       <c r="R40" t="n">
-        <v>6914048</v>
+        <v>6914008</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4879,7 +4871,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4889,12 +4881,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4921,10 +4908,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134095341</v>
+        <v>134095308</v>
       </c>
       <c r="B41" t="n">
-        <v>79347</v>
+        <v>79348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4956,13 +4943,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589783</v>
+        <v>589516</v>
       </c>
       <c r="R41" t="n">
-        <v>6914008</v>
+        <v>6914199</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4991,7 +4978,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5001,7 +4988,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5028,32 +5015,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134095308</v>
+        <v>134095322</v>
       </c>
       <c r="B42" t="n">
-        <v>79347</v>
+        <v>80481</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5063,13 +5050,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589516</v>
+        <v>589690</v>
       </c>
       <c r="R42" t="n">
-        <v>6914199</v>
+        <v>6914189</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5098,7 +5085,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5108,7 +5095,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5135,32 +5122,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134095322</v>
+        <v>134095251</v>
       </c>
       <c r="B43" t="n">
-        <v>80480</v>
+        <v>79348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5170,13 +5157,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589690</v>
+        <v>589524</v>
       </c>
       <c r="R43" t="n">
-        <v>6914189</v>
+        <v>6914076</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5205,7 +5192,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5215,7 +5202,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5245,7 +5232,7 @@
         <v>134095255</v>
       </c>
       <c r="B44" t="n">
-        <v>57964</v>
+        <v>57965</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,10 +5349,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134095251</v>
+        <v>134095311</v>
       </c>
       <c r="B45" t="n">
-        <v>79347</v>
+        <v>79348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5397,13 +5384,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589524</v>
+        <v>589554</v>
       </c>
       <c r="R45" t="n">
-        <v>6914076</v>
+        <v>6914221</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5432,7 +5419,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5442,7 +5429,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5469,10 +5456,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134095311</v>
+        <v>134095316</v>
       </c>
       <c r="B46" t="n">
-        <v>79347</v>
+        <v>79380</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5480,21 +5467,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5504,10 +5491,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589554</v>
+        <v>589589</v>
       </c>
       <c r="R46" t="n">
-        <v>6914221</v>
+        <v>6914177</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5539,7 +5526,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5549,7 +5536,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5579,7 +5566,7 @@
         <v>134095280</v>
       </c>
       <c r="B47" t="n">
-        <v>92215</v>
+        <v>92218</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5683,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134095316</v>
+        <v>134095318</v>
       </c>
       <c r="B48" t="n">
-        <v>79379</v>
+        <v>57965</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5694,34 +5681,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589589</v>
+        <v>589619</v>
       </c>
       <c r="R48" t="n">
-        <v>6914177</v>
+        <v>6914175</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5753,7 +5748,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5763,7 +5758,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5790,10 +5790,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134095273</v>
+        <v>134095355</v>
       </c>
       <c r="B49" t="n">
-        <v>79379</v>
+        <v>79380</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589415</v>
+        <v>589591</v>
       </c>
       <c r="R49" t="n">
-        <v>6914094</v>
+        <v>6914124</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5897,10 +5897,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134095264</v>
+        <v>134095250</v>
       </c>
       <c r="B50" t="n">
-        <v>57964</v>
+        <v>79380</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5908,42 +5908,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589558</v>
+        <v>589517</v>
       </c>
       <c r="R50" t="n">
-        <v>6914160</v>
+        <v>6914061</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5975,7 +5967,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5985,12 +5977,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6017,10 +6004,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134095250</v>
+        <v>134095264</v>
       </c>
       <c r="B51" t="n">
-        <v>79379</v>
+        <v>57965</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6028,34 +6015,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589517</v>
+        <v>589558</v>
       </c>
       <c r="R51" t="n">
-        <v>6914061</v>
+        <v>6914160</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6087,7 +6082,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6097,7 +6092,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6124,10 +6124,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134095326</v>
+        <v>134095273</v>
       </c>
       <c r="B52" t="n">
-        <v>79966</v>
+        <v>79380</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6135,21 +6135,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589658</v>
+        <v>589415</v>
       </c>
       <c r="R52" t="n">
-        <v>6914134</v>
+        <v>6914094</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,10 +6231,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134095318</v>
+        <v>134095326</v>
       </c>
       <c r="B53" t="n">
-        <v>57964</v>
+        <v>79967</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6242,42 +6242,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589619</v>
+        <v>589658</v>
       </c>
       <c r="R53" t="n">
-        <v>6914175</v>
+        <v>6914134</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6309,7 +6301,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6319,12 +6311,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6351,32 +6338,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134095355</v>
+        <v>134095296</v>
       </c>
       <c r="B54" t="n">
-        <v>79379</v>
+        <v>80413</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6386,10 +6373,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589591</v>
+        <v>589458</v>
       </c>
       <c r="R54" t="n">
-        <v>6914124</v>
+        <v>6914224</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6421,7 +6408,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6431,7 +6418,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6458,32 +6445,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134095296</v>
+        <v>134095277</v>
       </c>
       <c r="B55" t="n">
-        <v>80412</v>
+        <v>80326</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>392</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6493,10 +6480,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589458</v>
+        <v>589390</v>
       </c>
       <c r="R55" t="n">
-        <v>6914224</v>
+        <v>6914193</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6528,7 +6515,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6538,7 +6525,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6565,10 +6552,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134095272</v>
+        <v>134095353</v>
       </c>
       <c r="B56" t="n">
-        <v>79379</v>
+        <v>79348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6576,21 +6563,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6600,10 +6587,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589461</v>
+        <v>589598</v>
       </c>
       <c r="R56" t="n">
-        <v>6914134</v>
+        <v>6914117</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6635,7 +6622,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6645,7 +6632,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6672,10 +6659,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134095353</v>
+        <v>134095272</v>
       </c>
       <c r="B57" t="n">
-        <v>79347</v>
+        <v>79380</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6683,21 +6670,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6707,10 +6694,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589598</v>
+        <v>589461</v>
       </c>
       <c r="R57" t="n">
-        <v>6914117</v>
+        <v>6914134</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6742,7 +6729,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6752,7 +6739,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6779,32 +6766,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134095277</v>
+        <v>134095339</v>
       </c>
       <c r="B58" t="n">
-        <v>80325</v>
+        <v>79380</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>392</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6814,10 +6801,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589390</v>
+        <v>589780</v>
       </c>
       <c r="R58" t="n">
-        <v>6914193</v>
+        <v>6914027</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6849,7 +6836,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6859,7 +6846,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6889,7 +6876,7 @@
         <v>134095345</v>
       </c>
       <c r="B59" t="n">
-        <v>79379</v>
+        <v>79380</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6993,56 +6980,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134095356</v>
+        <v>134095304</v>
       </c>
       <c r="B60" t="n">
-        <v>57964</v>
+        <v>83316</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589578</v>
+        <v>589499</v>
       </c>
       <c r="R60" t="n">
-        <v>6914135</v>
+        <v>6914219</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7071,7 +7050,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7081,12 +7060,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7113,48 +7087,56 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134095304</v>
+        <v>134095356</v>
       </c>
       <c r="B61" t="n">
-        <v>83315</v>
+        <v>57965</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>589499</v>
+        <v>589578</v>
       </c>
       <c r="R61" t="n">
-        <v>6914219</v>
+        <v>6914135</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7183,7 +7165,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7193,7 +7175,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7220,10 +7207,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134095339</v>
+        <v>134095344</v>
       </c>
       <c r="B62" t="n">
-        <v>79379</v>
+        <v>79380</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7255,10 +7242,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>589780</v>
+        <v>589713</v>
       </c>
       <c r="R62" t="n">
-        <v>6914027</v>
+        <v>6914030</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7290,7 +7277,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7300,7 +7287,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7330,7 +7317,7 @@
         <v>134095283</v>
       </c>
       <c r="B63" t="n">
-        <v>79347</v>
+        <v>79348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7437,7 +7424,7 @@
         <v>134095333</v>
       </c>
       <c r="B64" t="n">
-        <v>91955</v>
+        <v>91958</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7544,7 +7531,7 @@
         <v>134095253</v>
       </c>
       <c r="B65" t="n">
-        <v>79379</v>
+        <v>79380</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7648,10 +7635,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134095344</v>
+        <v>134095310</v>
       </c>
       <c r="B66" t="n">
-        <v>79379</v>
+        <v>83333</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7659,21 +7646,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7683,10 +7670,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>589713</v>
+        <v>589530</v>
       </c>
       <c r="R66" t="n">
-        <v>6914030</v>
+        <v>6914215</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7718,7 +7705,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7728,7 +7715,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7755,10 +7742,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134095310</v>
+        <v>134095282</v>
       </c>
       <c r="B67" t="n">
-        <v>83332</v>
+        <v>89328</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7766,21 +7753,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7790,10 +7777,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589530</v>
+        <v>589375</v>
       </c>
       <c r="R67" t="n">
-        <v>6914215</v>
+        <v>6914205</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7825,7 +7812,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7835,7 +7822,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7865,7 +7852,7 @@
         <v>134095275</v>
       </c>
       <c r="B68" t="n">
-        <v>79379</v>
+        <v>79380</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7969,10 +7956,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134095271</v>
+        <v>134095262</v>
       </c>
       <c r="B69" t="n">
-        <v>79347</v>
+        <v>79348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8004,10 +7991,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>589468</v>
+        <v>589551</v>
       </c>
       <c r="R69" t="n">
-        <v>6914148</v>
+        <v>6914130</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8039,7 +8026,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8049,7 +8036,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8076,10 +8063,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134095262</v>
+        <v>134095271</v>
       </c>
       <c r="B70" t="n">
-        <v>79347</v>
+        <v>79348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8111,10 +8098,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589551</v>
+        <v>589468</v>
       </c>
       <c r="R70" t="n">
-        <v>6914130</v>
+        <v>6914148</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8146,7 +8133,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8156,7 +8143,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8183,32 +8170,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134095282</v>
+        <v>134095297</v>
       </c>
       <c r="B71" t="n">
-        <v>89326</v>
+        <v>92126</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>510</v>
+        <v>1503</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8218,10 +8205,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>589375</v>
+        <v>589461</v>
       </c>
       <c r="R71" t="n">
-        <v>6914205</v>
+        <v>6914228</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8253,7 +8240,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8263,7 +8250,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8272,6 +8259,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8290,32 +8278,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134095297</v>
+        <v>134095288</v>
       </c>
       <c r="B72" t="n">
-        <v>92123</v>
+        <v>91958</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>1205</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8325,10 +8313,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>589461</v>
+        <v>589439</v>
       </c>
       <c r="R72" t="n">
-        <v>6914228</v>
+        <v>6914221</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8360,7 +8348,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8370,7 +8358,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8379,7 +8367,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8398,10 +8385,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134095340</v>
+        <v>134095351</v>
       </c>
       <c r="B73" t="n">
-        <v>57964</v>
+        <v>91947</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8409,42 +8396,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>589780</v>
+        <v>589610</v>
       </c>
       <c r="R73" t="n">
-        <v>6914012</v>
+        <v>6914116</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8476,7 +8455,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8486,12 +8465,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8518,10 +8492,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134095352</v>
+        <v>134095286</v>
       </c>
       <c r="B74" t="n">
-        <v>91944</v>
+        <v>79348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8529,21 +8503,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8553,10 +8527,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589608</v>
+        <v>589414</v>
       </c>
       <c r="R74" t="n">
-        <v>6914114</v>
+        <v>6914214</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8588,7 +8562,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8598,7 +8572,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8625,32 +8599,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134095288</v>
+        <v>134095352</v>
       </c>
       <c r="B75" t="n">
-        <v>91955</v>
+        <v>91947</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8660,10 +8634,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>589439</v>
+        <v>589608</v>
       </c>
       <c r="R75" t="n">
-        <v>6914221</v>
+        <v>6914114</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8695,7 +8669,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8705,7 +8679,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8732,10 +8706,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134095351</v>
+        <v>134095274</v>
       </c>
       <c r="B76" t="n">
-        <v>91944</v>
+        <v>79380</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8743,21 +8717,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8767,7 +8741,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>589610</v>
+        <v>589385</v>
       </c>
       <c r="R76" t="n">
         <v>6914116</v>
@@ -8802,7 +8776,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8812,7 +8786,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8839,10 +8813,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134095286</v>
+        <v>134095321</v>
       </c>
       <c r="B77" t="n">
-        <v>79347</v>
+        <v>57965</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8850,34 +8824,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>589414</v>
+        <v>589618</v>
       </c>
       <c r="R77" t="n">
-        <v>6914214</v>
+        <v>6914190</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8909,7 +8891,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8919,7 +8901,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8946,10 +8933,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134095343</v>
+        <v>134095319</v>
       </c>
       <c r="B78" t="n">
-        <v>79379</v>
+        <v>79380</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8981,10 +8968,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>589720</v>
+        <v>589626</v>
       </c>
       <c r="R78" t="n">
-        <v>6914011</v>
+        <v>6914176</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9016,7 +9003,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9026,7 +9013,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9053,10 +9040,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134095269</v>
+        <v>134095343</v>
       </c>
       <c r="B79" t="n">
-        <v>79347</v>
+        <v>79380</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9064,21 +9051,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9088,10 +9075,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589498</v>
+        <v>589720</v>
       </c>
       <c r="R79" t="n">
-        <v>6914160</v>
+        <v>6914011</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9123,7 +9110,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9133,7 +9120,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9160,10 +9147,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134095274</v>
+        <v>134095259</v>
       </c>
       <c r="B80" t="n">
-        <v>79379</v>
+        <v>89328</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9171,21 +9158,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9195,10 +9182,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589385</v>
+        <v>589496</v>
       </c>
       <c r="R80" t="n">
-        <v>6914116</v>
+        <v>6914098</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9230,7 +9217,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9240,7 +9227,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9267,10 +9254,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134095321</v>
+        <v>134095269</v>
       </c>
       <c r="B81" t="n">
-        <v>57964</v>
+        <v>79348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9278,42 +9265,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>589618</v>
+        <v>589498</v>
       </c>
       <c r="R81" t="n">
-        <v>6914190</v>
+        <v>6914160</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9345,7 +9324,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9355,12 +9334,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9387,10 +9361,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134095319</v>
+        <v>134095314</v>
       </c>
       <c r="B82" t="n">
-        <v>79379</v>
+        <v>79380</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9422,10 +9396,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>589626</v>
+        <v>589578</v>
       </c>
       <c r="R82" t="n">
-        <v>6914176</v>
+        <v>6914200</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9457,7 +9431,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9467,7 +9441,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9494,10 +9468,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134095259</v>
+        <v>134095342</v>
       </c>
       <c r="B83" t="n">
-        <v>89326</v>
+        <v>79380</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9505,21 +9479,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9529,10 +9503,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>589496</v>
+        <v>589787</v>
       </c>
       <c r="R83" t="n">
-        <v>6914098</v>
+        <v>6914002</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9564,7 +9538,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9574,7 +9548,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9601,10 +9575,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134095314</v>
+        <v>134095358</v>
       </c>
       <c r="B84" t="n">
-        <v>79379</v>
+        <v>57965</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9612,34 +9586,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589578</v>
+        <v>589566</v>
       </c>
       <c r="R84" t="n">
-        <v>6914200</v>
+        <v>6914072</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9671,7 +9653,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9681,7 +9663,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9708,10 +9695,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134095266</v>
+        <v>134095302</v>
       </c>
       <c r="B85" t="n">
-        <v>79379</v>
+        <v>80453</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9719,21 +9706,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9743,10 +9730,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589544</v>
+        <v>589510</v>
       </c>
       <c r="R85" t="n">
-        <v>6914176</v>
+        <v>6914242</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9778,7 +9765,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9788,7 +9775,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9815,10 +9802,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134095329</v>
+        <v>134095257</v>
       </c>
       <c r="B86" t="n">
-        <v>57964</v>
+        <v>79380</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9826,42 +9813,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>589690</v>
+        <v>589500</v>
       </c>
       <c r="R86" t="n">
-        <v>6914133</v>
+        <v>6914077</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9893,7 +9872,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9903,12 +9882,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9935,53 +9909,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134095358</v>
+        <v>134095307</v>
       </c>
       <c r="B87" t="n">
-        <v>57964</v>
+        <v>80481</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>589566</v>
+        <v>589520</v>
       </c>
       <c r="R87" t="n">
-        <v>6914072</v>
+        <v>6914195</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10013,7 +9979,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10023,12 +9989,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10055,10 +10016,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134095302</v>
+        <v>134095266</v>
       </c>
       <c r="B88" t="n">
-        <v>80452</v>
+        <v>79380</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10066,21 +10027,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10090,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>589510</v>
+        <v>589544</v>
       </c>
       <c r="R88" t="n">
-        <v>6914242</v>
+        <v>6914176</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10125,7 +10086,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10135,7 +10096,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10162,32 +10123,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134095331</v>
+        <v>134095317</v>
       </c>
       <c r="B89" t="n">
-        <v>99165</v>
+        <v>79348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10197,10 +10158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589707</v>
+        <v>589590</v>
       </c>
       <c r="R89" t="n">
-        <v>6914116</v>
+        <v>6914172</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10232,7 +10193,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10242,12 +10203,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>190 ex</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10274,32 +10230,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134095257</v>
+        <v>134095263</v>
       </c>
       <c r="B90" t="n">
-        <v>79379</v>
+        <v>80357</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10309,10 +10265,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589500</v>
+        <v>589541</v>
       </c>
       <c r="R90" t="n">
-        <v>6914077</v>
+        <v>6914140</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10344,7 +10300,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10354,7 +10310,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10381,10 +10337,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134095342</v>
+        <v>134095267</v>
       </c>
       <c r="B91" t="n">
-        <v>79379</v>
+        <v>79380</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10416,10 +10372,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>589787</v>
+        <v>589498</v>
       </c>
       <c r="R91" t="n">
-        <v>6914002</v>
+        <v>6914160</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10451,7 +10407,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10461,7 +10417,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10488,45 +10444,53 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134095307</v>
+        <v>134095328</v>
       </c>
       <c r="B92" t="n">
-        <v>80480</v>
+        <v>57965</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>589520</v>
+        <v>589682</v>
       </c>
       <c r="R92" t="n">
-        <v>6914195</v>
+        <v>6914127</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10558,7 +10522,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10568,14 +10532,19 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Påbörjade bohål i grantickerötad granhögstubbe. Hålen sitter 1.5 meter respektive 2.5 m ovan mark.</t>
         </is>
       </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG92" t="b">
         <v>0</v>
@@ -10595,10 +10564,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134095267</v>
+        <v>134095340</v>
       </c>
       <c r="B93" t="n">
-        <v>79379</v>
+        <v>57965</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10606,34 +10575,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>589498</v>
+        <v>589780</v>
       </c>
       <c r="R93" t="n">
-        <v>6914160</v>
+        <v>6914012</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10665,7 +10642,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10675,7 +10652,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10702,32 +10684,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134095317</v>
+        <v>134095331</v>
       </c>
       <c r="B94" t="n">
-        <v>79347</v>
+        <v>99168</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10737,10 +10719,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>589590</v>
+        <v>589707</v>
       </c>
       <c r="R94" t="n">
-        <v>6914172</v>
+        <v>6914116</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10772,7 +10754,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10782,7 +10764,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>190 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10809,45 +10796,53 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134095263</v>
+        <v>134095329</v>
       </c>
       <c r="B95" t="n">
-        <v>80356</v>
+        <v>57965</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>589541</v>
+        <v>589690</v>
       </c>
       <c r="R95" t="n">
-        <v>6914140</v>
+        <v>6914133</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10879,7 +10874,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10889,7 +10884,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10919,7 +10919,7 @@
         <v>134095312</v>
       </c>
       <c r="B96" t="n">
-        <v>57964</v>
+        <v>57965</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 59973-2025 artfynd.xlsx
+++ b/artfynd/A 59973-2025 artfynd.xlsx
@@ -1116,32 +1116,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134095313</v>
+        <v>134095305</v>
       </c>
       <c r="B6" t="n">
-        <v>79380</v>
+        <v>80413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589577</v>
+        <v>589501</v>
       </c>
       <c r="R6" t="n">
-        <v>6914208</v>
+        <v>6914218</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1223,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134095248</v>
+        <v>134095285</v>
       </c>
       <c r="B7" t="n">
         <v>79380</v>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589533</v>
+        <v>589377</v>
       </c>
       <c r="R7" t="n">
-        <v>6914053</v>
+        <v>6914229</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,32 +1330,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134095305</v>
+        <v>134095260</v>
       </c>
       <c r="B8" t="n">
-        <v>80413</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589501</v>
+        <v>589507</v>
       </c>
       <c r="R8" t="n">
-        <v>6914218</v>
+        <v>6914122</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134095285</v>
+        <v>134095248</v>
       </c>
       <c r="B9" t="n">
         <v>79380</v>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589377</v>
+        <v>589533</v>
       </c>
       <c r="R9" t="n">
-        <v>6914229</v>
+        <v>6914053</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134095260</v>
+        <v>134095313</v>
       </c>
       <c r="B10" t="n">
-        <v>79348</v>
+        <v>79380</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589507</v>
+        <v>589577</v>
       </c>
       <c r="R10" t="n">
-        <v>6914122</v>
+        <v>6914208</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,32 +1651,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134095293</v>
+        <v>134095289</v>
       </c>
       <c r="B11" t="n">
-        <v>80413</v>
+        <v>79348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589461</v>
+        <v>589423</v>
       </c>
       <c r="R11" t="n">
-        <v>6914225</v>
+        <v>6914227</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,32 +1758,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134095289</v>
+        <v>134095270</v>
       </c>
       <c r="B12" t="n">
-        <v>79348</v>
+        <v>91910</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589423</v>
+        <v>589483</v>
       </c>
       <c r="R12" t="n">
-        <v>6914227</v>
+        <v>6914142</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,32 +1865,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134095291</v>
+        <v>134095293</v>
       </c>
       <c r="B13" t="n">
-        <v>91947</v>
+        <v>80413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589424</v>
+        <v>589461</v>
       </c>
       <c r="R13" t="n">
-        <v>6914230</v>
+        <v>6914225</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,32 +1972,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134095270</v>
+        <v>134095346</v>
       </c>
       <c r="B14" t="n">
-        <v>91910</v>
+        <v>79380</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589483</v>
+        <v>589671</v>
       </c>
       <c r="R14" t="n">
-        <v>6914142</v>
+        <v>6914046</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134095346</v>
+        <v>134095291</v>
       </c>
       <c r="B15" t="n">
-        <v>79380</v>
+        <v>91947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589671</v>
+        <v>589424</v>
       </c>
       <c r="R15" t="n">
-        <v>6914046</v>
+        <v>6914230</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,32 +2186,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134095309</v>
+        <v>134095324</v>
       </c>
       <c r="B16" t="n">
-        <v>80413</v>
+        <v>79380</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589523</v>
+        <v>589658</v>
       </c>
       <c r="R16" t="n">
-        <v>6914208</v>
+        <v>6914166</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134095337</v>
+        <v>134095261</v>
       </c>
       <c r="B17" t="n">
-        <v>91947</v>
+        <v>79380</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,21 +2304,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589774</v>
+        <v>589508</v>
       </c>
       <c r="R17" t="n">
-        <v>6914028</v>
+        <v>6914122</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,32 +2400,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134095261</v>
+        <v>134095309</v>
       </c>
       <c r="B18" t="n">
-        <v>79380</v>
+        <v>80413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589508</v>
+        <v>589523</v>
       </c>
       <c r="R18" t="n">
-        <v>6914122</v>
+        <v>6914208</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,7 +2507,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134095324</v>
+        <v>134095252</v>
       </c>
       <c r="B19" t="n">
         <v>79380</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589658</v>
+        <v>589531</v>
       </c>
       <c r="R19" t="n">
-        <v>6914166</v>
+        <v>6914096</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2614,32 +2614,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134095252</v>
+        <v>134095281</v>
       </c>
       <c r="B20" t="n">
-        <v>79380</v>
+        <v>92379</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589531</v>
+        <v>589375</v>
       </c>
       <c r="R20" t="n">
-        <v>6914096</v>
+        <v>6914203</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,32 +2721,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134095281</v>
+        <v>134095337</v>
       </c>
       <c r="B21" t="n">
-        <v>92379</v>
+        <v>91947</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589375</v>
+        <v>589774</v>
       </c>
       <c r="R21" t="n">
-        <v>6914203</v>
+        <v>6914028</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,7 +2948,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134095350</v>
+        <v>134095335</v>
       </c>
       <c r="B23" t="n">
         <v>79380</v>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589620</v>
+        <v>589737</v>
       </c>
       <c r="R23" t="n">
-        <v>6914079</v>
+        <v>6914072</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,7 +3055,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134095335</v>
+        <v>134095350</v>
       </c>
       <c r="B24" t="n">
         <v>79380</v>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589737</v>
+        <v>589620</v>
       </c>
       <c r="R24" t="n">
-        <v>6914072</v>
+        <v>6914079</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3269,45 +3269,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134095292</v>
+        <v>134095359</v>
       </c>
       <c r="B26" t="n">
-        <v>80453</v>
+        <v>57152</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589461</v>
+        <v>589567</v>
       </c>
       <c r="R26" t="n">
-        <v>6914224</v>
+        <v>6914071</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3339,7 +3347,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3349,7 +3357,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3376,10 +3384,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134095294</v>
+        <v>134095336</v>
       </c>
       <c r="B27" t="n">
-        <v>80453</v>
+        <v>91947</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,21 +3395,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3411,13 +3419,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589458</v>
+        <v>589761</v>
       </c>
       <c r="R27" t="n">
-        <v>6914224</v>
+        <v>6914026</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3446,7 +3454,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3456,7 +3464,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3590,53 +3598,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134095359</v>
+        <v>134095292</v>
       </c>
       <c r="B29" t="n">
-        <v>57152</v>
+        <v>80453</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589567</v>
+        <v>589461</v>
       </c>
       <c r="R29" t="n">
-        <v>6914071</v>
+        <v>6914224</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134095336</v>
+        <v>134095294</v>
       </c>
       <c r="B30" t="n">
-        <v>91947</v>
+        <v>80453</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589761</v>
+        <v>589458</v>
       </c>
       <c r="R30" t="n">
-        <v>6914026</v>
+        <v>6914224</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3919,10 +3919,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134095287</v>
+        <v>134095303</v>
       </c>
       <c r="B32" t="n">
-        <v>80453</v>
+        <v>89328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589437</v>
+        <v>589501</v>
       </c>
       <c r="R32" t="n">
-        <v>6914217</v>
+        <v>6914225</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4133,10 +4133,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134095303</v>
+        <v>134095287</v>
       </c>
       <c r="B34" t="n">
-        <v>89328</v>
+        <v>80453</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589501</v>
+        <v>589437</v>
       </c>
       <c r="R34" t="n">
-        <v>6914225</v>
+        <v>6914217</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4574,53 +4574,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134095348</v>
+        <v>134095320</v>
       </c>
       <c r="B38" t="n">
-        <v>57965</v>
+        <v>80481</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589625</v>
+        <v>589619</v>
       </c>
       <c r="R38" t="n">
-        <v>6914048</v>
+        <v>6914197</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4652,7 +4644,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4662,12 +4654,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4694,45 +4681,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134095320</v>
+        <v>134095348</v>
       </c>
       <c r="B39" t="n">
-        <v>80481</v>
+        <v>57965</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589619</v>
+        <v>589625</v>
       </c>
       <c r="R39" t="n">
-        <v>6914197</v>
+        <v>6914048</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4764,7 +4759,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4774,7 +4769,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5015,32 +5015,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134095322</v>
+        <v>134095251</v>
       </c>
       <c r="B42" t="n">
-        <v>80481</v>
+        <v>79348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5050,13 +5050,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589690</v>
+        <v>589524</v>
       </c>
       <c r="R42" t="n">
-        <v>6914189</v>
+        <v>6914076</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5122,10 +5122,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134095251</v>
+        <v>134095255</v>
       </c>
       <c r="B43" t="n">
-        <v>79348</v>
+        <v>57965</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5133,37 +5133,45 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589524</v>
+        <v>589512</v>
       </c>
       <c r="R43" t="n">
-        <v>6914076</v>
+        <v>6914087</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5192,7 +5200,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5202,7 +5210,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5229,53 +5242,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134095255</v>
+        <v>134095322</v>
       </c>
       <c r="B44" t="n">
-        <v>57965</v>
+        <v>80481</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589512</v>
+        <v>589690</v>
       </c>
       <c r="R44" t="n">
-        <v>6914087</v>
+        <v>6914189</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5307,7 +5312,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5317,12 +5322,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:08</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5349,10 +5349,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134095311</v>
+        <v>134095280</v>
       </c>
       <c r="B45" t="n">
-        <v>79348</v>
+        <v>92218</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589554</v>
+        <v>589373</v>
       </c>
       <c r="R45" t="n">
-        <v>6914221</v>
+        <v>6914203</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5456,10 +5456,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134095316</v>
+        <v>134095311</v>
       </c>
       <c r="B46" t="n">
-        <v>79380</v>
+        <v>79348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5467,21 +5467,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589589</v>
+        <v>589554</v>
       </c>
       <c r="R46" t="n">
-        <v>6914177</v>
+        <v>6914221</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5563,10 +5563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134095280</v>
+        <v>134095316</v>
       </c>
       <c r="B47" t="n">
-        <v>92218</v>
+        <v>79380</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5574,21 +5574,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589373</v>
+        <v>589589</v>
       </c>
       <c r="R47" t="n">
-        <v>6914203</v>
+        <v>6914177</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134095318</v>
+        <v>134095273</v>
       </c>
       <c r="B48" t="n">
-        <v>57965</v>
+        <v>79380</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,42 +5681,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589619</v>
+        <v>589415</v>
       </c>
       <c r="R48" t="n">
-        <v>6914175</v>
+        <v>6914094</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5748,7 +5740,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5758,12 +5750,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5790,10 +5777,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134095355</v>
+        <v>134095326</v>
       </c>
       <c r="B49" t="n">
-        <v>79380</v>
+        <v>79967</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5801,21 +5788,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5825,10 +5812,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589591</v>
+        <v>589658</v>
       </c>
       <c r="R49" t="n">
-        <v>6914124</v>
+        <v>6914134</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5860,7 +5847,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5870,7 +5857,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5897,7 +5884,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134095250</v>
+        <v>134095355</v>
       </c>
       <c r="B50" t="n">
         <v>79380</v>
@@ -5932,10 +5919,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589517</v>
+        <v>589591</v>
       </c>
       <c r="R50" t="n">
-        <v>6914061</v>
+        <v>6914124</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5967,7 +5954,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5977,7 +5964,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6004,10 +5991,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134095264</v>
+        <v>134095250</v>
       </c>
       <c r="B51" t="n">
-        <v>57965</v>
+        <v>79380</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6015,42 +6002,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589558</v>
+        <v>589517</v>
       </c>
       <c r="R51" t="n">
-        <v>6914160</v>
+        <v>6914061</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6082,7 +6061,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6092,12 +6071,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6124,10 +6098,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134095273</v>
+        <v>134095318</v>
       </c>
       <c r="B52" t="n">
-        <v>79380</v>
+        <v>57965</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6135,34 +6109,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589415</v>
+        <v>589619</v>
       </c>
       <c r="R52" t="n">
-        <v>6914094</v>
+        <v>6914175</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6194,7 +6176,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6204,7 +6186,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,10 +6218,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134095326</v>
+        <v>134095264</v>
       </c>
       <c r="B53" t="n">
-        <v>79967</v>
+        <v>57965</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6242,34 +6229,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589658</v>
+        <v>589558</v>
       </c>
       <c r="R53" t="n">
-        <v>6914134</v>
+        <v>6914160</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6301,7 +6296,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6311,7 +6306,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6338,32 +6338,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134095296</v>
+        <v>134095353</v>
       </c>
       <c r="B54" t="n">
-        <v>80413</v>
+        <v>79348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6373,10 +6373,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589458</v>
+        <v>589598</v>
       </c>
       <c r="R54" t="n">
-        <v>6914224</v>
+        <v>6914117</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6445,32 +6445,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134095277</v>
+        <v>134095296</v>
       </c>
       <c r="B55" t="n">
-        <v>80326</v>
+        <v>80413</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>392</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589390</v>
+        <v>589458</v>
       </c>
       <c r="R55" t="n">
-        <v>6914193</v>
+        <v>6914224</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6552,32 +6552,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134095353</v>
+        <v>134095277</v>
       </c>
       <c r="B56" t="n">
-        <v>79348</v>
+        <v>80326</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589598</v>
+        <v>589390</v>
       </c>
       <c r="R56" t="n">
-        <v>6914117</v>
+        <v>6914193</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6766,7 +6766,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134095339</v>
+        <v>134095345</v>
       </c>
       <c r="B58" t="n">
         <v>79380</v>
@@ -6801,10 +6801,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589780</v>
+        <v>589680</v>
       </c>
       <c r="R58" t="n">
-        <v>6914027</v>
+        <v>6914079</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6873,32 +6873,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134095345</v>
+        <v>134095304</v>
       </c>
       <c r="B59" t="n">
-        <v>79380</v>
+        <v>83316</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6439</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589680</v>
+        <v>589499</v>
       </c>
       <c r="R59" t="n">
-        <v>6914079</v>
+        <v>6914219</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6980,32 +6980,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134095304</v>
+        <v>134095339</v>
       </c>
       <c r="B60" t="n">
-        <v>83316</v>
+        <v>79380</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589499</v>
+        <v>589780</v>
       </c>
       <c r="R60" t="n">
-        <v>6914219</v>
+        <v>6914027</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7314,32 +7314,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134095283</v>
+        <v>134095333</v>
       </c>
       <c r="B63" t="n">
-        <v>79348</v>
+        <v>91958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589376</v>
+        <v>589727</v>
       </c>
       <c r="R63" t="n">
-        <v>6914228</v>
+        <v>6914106</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7421,32 +7421,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134095333</v>
+        <v>134095283</v>
       </c>
       <c r="B64" t="n">
-        <v>91958</v>
+        <v>79348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>589727</v>
+        <v>589376</v>
       </c>
       <c r="R64" t="n">
-        <v>6914106</v>
+        <v>6914228</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7742,32 +7742,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134095282</v>
+        <v>134095297</v>
       </c>
       <c r="B67" t="n">
-        <v>89328</v>
+        <v>92126</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>510</v>
+        <v>1503</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7777,10 +7777,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589375</v>
+        <v>589461</v>
       </c>
       <c r="R67" t="n">
-        <v>6914205</v>
+        <v>6914228</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7831,6 +7831,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7849,10 +7850,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134095275</v>
+        <v>134095271</v>
       </c>
       <c r="B68" t="n">
-        <v>79380</v>
+        <v>79348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7860,21 +7861,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7884,10 +7885,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>589368</v>
+        <v>589468</v>
       </c>
       <c r="R68" t="n">
-        <v>6914134</v>
+        <v>6914148</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7919,7 +7920,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7929,7 +7930,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7956,10 +7957,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134095262</v>
+        <v>134095282</v>
       </c>
       <c r="B69" t="n">
-        <v>79348</v>
+        <v>89328</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7967,21 +7968,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7991,10 +7992,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>589551</v>
+        <v>589375</v>
       </c>
       <c r="R69" t="n">
-        <v>6914130</v>
+        <v>6914205</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8026,7 +8027,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8036,7 +8037,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8063,7 +8064,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134095271</v>
+        <v>134095262</v>
       </c>
       <c r="B70" t="n">
         <v>79348</v>
@@ -8098,10 +8099,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589468</v>
+        <v>589551</v>
       </c>
       <c r="R70" t="n">
-        <v>6914148</v>
+        <v>6914130</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8133,7 +8134,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8143,7 +8144,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8170,32 +8171,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134095297</v>
+        <v>134095275</v>
       </c>
       <c r="B71" t="n">
-        <v>92126</v>
+        <v>79380</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1503</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8205,10 +8206,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>589461</v>
+        <v>589368</v>
       </c>
       <c r="R71" t="n">
-        <v>6914228</v>
+        <v>6914134</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8240,7 +8241,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8250,7 +8251,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8259,7 +8260,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8385,7 +8385,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134095351</v>
+        <v>134095352</v>
       </c>
       <c r="B73" t="n">
         <v>91947</v>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>589610</v>
+        <v>589608</v>
       </c>
       <c r="R73" t="n">
-        <v>6914116</v>
+        <v>6914114</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8492,10 +8492,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134095286</v>
+        <v>134095351</v>
       </c>
       <c r="B74" t="n">
-        <v>79348</v>
+        <v>91947</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8503,21 +8503,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589414</v>
+        <v>589610</v>
       </c>
       <c r="R74" t="n">
-        <v>6914214</v>
+        <v>6914116</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8599,10 +8599,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134095352</v>
+        <v>134095286</v>
       </c>
       <c r="B75" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8610,21 +8610,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8634,10 +8634,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>589608</v>
+        <v>589414</v>
       </c>
       <c r="R75" t="n">
-        <v>6914114</v>
+        <v>6914214</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8706,7 +8706,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134095274</v>
+        <v>134095343</v>
       </c>
       <c r="B76" t="n">
         <v>79380</v>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>589385</v>
+        <v>589720</v>
       </c>
       <c r="R76" t="n">
-        <v>6914116</v>
+        <v>6914011</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8813,10 +8813,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134095321</v>
+        <v>134095274</v>
       </c>
       <c r="B77" t="n">
-        <v>57965</v>
+        <v>79380</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8824,42 +8824,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>589618</v>
+        <v>589385</v>
       </c>
       <c r="R77" t="n">
-        <v>6914190</v>
+        <v>6914116</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8891,7 +8883,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8901,12 +8893,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8933,10 +8920,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134095319</v>
+        <v>134095321</v>
       </c>
       <c r="B78" t="n">
-        <v>79380</v>
+        <v>57965</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8944,34 +8931,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>589626</v>
+        <v>589618</v>
       </c>
       <c r="R78" t="n">
-        <v>6914176</v>
+        <v>6914190</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9003,7 +8998,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9013,7 +9008,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9040,7 +9040,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134095343</v>
+        <v>134095319</v>
       </c>
       <c r="B79" t="n">
         <v>79380</v>
@@ -9075,10 +9075,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589720</v>
+        <v>589626</v>
       </c>
       <c r="R79" t="n">
-        <v>6914011</v>
+        <v>6914176</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9468,10 +9468,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134095342</v>
+        <v>134095358</v>
       </c>
       <c r="B83" t="n">
-        <v>79380</v>
+        <v>57965</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9479,34 +9479,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>589787</v>
+        <v>589566</v>
       </c>
       <c r="R83" t="n">
-        <v>6914002</v>
+        <v>6914072</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9538,7 +9546,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9548,7 +9556,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9575,10 +9588,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134095358</v>
+        <v>134095302</v>
       </c>
       <c r="B84" t="n">
-        <v>57965</v>
+        <v>80453</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9586,42 +9599,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589566</v>
+        <v>589510</v>
       </c>
       <c r="R84" t="n">
-        <v>6914072</v>
+        <v>6914242</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9653,7 +9658,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9663,12 +9668,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9695,10 +9695,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134095302</v>
+        <v>134095257</v>
       </c>
       <c r="B85" t="n">
-        <v>80453</v>
+        <v>79380</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9706,21 +9706,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9730,10 +9730,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589510</v>
+        <v>589500</v>
       </c>
       <c r="R85" t="n">
-        <v>6914242</v>
+        <v>6914077</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9802,32 +9802,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134095257</v>
+        <v>134095307</v>
       </c>
       <c r="B86" t="n">
-        <v>79380</v>
+        <v>80481</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>6461</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9837,10 +9837,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>589500</v>
+        <v>589520</v>
       </c>
       <c r="R86" t="n">
-        <v>6914077</v>
+        <v>6914195</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9909,32 +9909,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134095307</v>
+        <v>134095266</v>
       </c>
       <c r="B87" t="n">
-        <v>80481</v>
+        <v>79380</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6461</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9944,10 +9944,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>589520</v>
+        <v>589544</v>
       </c>
       <c r="R87" t="n">
-        <v>6914195</v>
+        <v>6914176</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10016,7 +10016,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134095266</v>
+        <v>134095342</v>
       </c>
       <c r="B88" t="n">
         <v>79380</v>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>589544</v>
+        <v>589787</v>
       </c>
       <c r="R88" t="n">
-        <v>6914176</v>
+        <v>6914002</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10123,10 +10123,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134095317</v>
+        <v>134095267</v>
       </c>
       <c r="B89" t="n">
-        <v>79348</v>
+        <v>79380</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10134,21 +10134,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589590</v>
+        <v>589498</v>
       </c>
       <c r="R89" t="n">
-        <v>6914172</v>
+        <v>6914160</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10337,10 +10337,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134095267</v>
+        <v>134095317</v>
       </c>
       <c r="B91" t="n">
-        <v>79380</v>
+        <v>79348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10348,21 +10348,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10372,10 +10372,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>589498</v>
+        <v>589590</v>
       </c>
       <c r="R91" t="n">
-        <v>6914160</v>
+        <v>6914172</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 59973-2025 artfynd.xlsx
+++ b/artfynd/A 59973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134095278</v>
       </c>
       <c r="B2" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>134095276</v>
       </c>
       <c r="B3" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>134095306</v>
       </c>
       <c r="B4" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>134095299</v>
       </c>
       <c r="B5" t="n">
-        <v>80413</v>
+        <v>80423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,32 +1116,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134095305</v>
+        <v>134095248</v>
       </c>
       <c r="B6" t="n">
-        <v>80413</v>
+        <v>79390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589501</v>
+        <v>589533</v>
       </c>
       <c r="R6" t="n">
-        <v>6914218</v>
+        <v>6914053</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134095285</v>
+        <v>134095305</v>
       </c>
       <c r="B7" t="n">
-        <v>79380</v>
+        <v>80423</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589377</v>
+        <v>589501</v>
       </c>
       <c r="R7" t="n">
-        <v>6914229</v>
+        <v>6914218</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134095260</v>
+        <v>134095285</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>79390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589507</v>
+        <v>589377</v>
       </c>
       <c r="R8" t="n">
-        <v>6914122</v>
+        <v>6914229</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134095248</v>
+        <v>134095313</v>
       </c>
       <c r="B9" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589533</v>
+        <v>589577</v>
       </c>
       <c r="R9" t="n">
-        <v>6914053</v>
+        <v>6914208</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134095313</v>
+        <v>134095260</v>
       </c>
       <c r="B10" t="n">
-        <v>79380</v>
+        <v>79358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589577</v>
+        <v>589507</v>
       </c>
       <c r="R10" t="n">
-        <v>6914208</v>
+        <v>6914122</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,32 +1651,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134095289</v>
+        <v>134095270</v>
       </c>
       <c r="B11" t="n">
-        <v>79348</v>
+        <v>91920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589423</v>
+        <v>589483</v>
       </c>
       <c r="R11" t="n">
-        <v>6914227</v>
+        <v>6914142</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134095270</v>
+        <v>134095293</v>
       </c>
       <c r="B12" t="n">
-        <v>91910</v>
+        <v>80423</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589483</v>
+        <v>589461</v>
       </c>
       <c r="R12" t="n">
-        <v>6914142</v>
+        <v>6914225</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,32 +1865,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134095293</v>
+        <v>134095346</v>
       </c>
       <c r="B13" t="n">
-        <v>80413</v>
+        <v>79390</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589461</v>
+        <v>589671</v>
       </c>
       <c r="R13" t="n">
-        <v>6914225</v>
+        <v>6914046</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134095346</v>
+        <v>134095289</v>
       </c>
       <c r="B14" t="n">
-        <v>79380</v>
+        <v>79358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589671</v>
+        <v>589423</v>
       </c>
       <c r="R14" t="n">
-        <v>6914046</v>
+        <v>6914227</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,7 +2082,7 @@
         <v>134095291</v>
       </c>
       <c r="B15" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>134095324</v>
       </c>
       <c r="B16" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,32 +2293,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134095261</v>
+        <v>134095309</v>
       </c>
       <c r="B17" t="n">
-        <v>79380</v>
+        <v>80423</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589508</v>
+        <v>589523</v>
       </c>
       <c r="R17" t="n">
-        <v>6914122</v>
+        <v>6914208</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,32 +2400,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134095309</v>
+        <v>134095252</v>
       </c>
       <c r="B18" t="n">
-        <v>80413</v>
+        <v>79390</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589523</v>
+        <v>589531</v>
       </c>
       <c r="R18" t="n">
-        <v>6914208</v>
+        <v>6914096</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,32 +2507,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134095252</v>
+        <v>134095281</v>
       </c>
       <c r="B19" t="n">
-        <v>79380</v>
+        <v>92389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589531</v>
+        <v>589375</v>
       </c>
       <c r="R19" t="n">
-        <v>6914096</v>
+        <v>6914203</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2614,32 +2614,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134095281</v>
+        <v>134095337</v>
       </c>
       <c r="B20" t="n">
-        <v>92379</v>
+        <v>91957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589375</v>
+        <v>589774</v>
       </c>
       <c r="R20" t="n">
-        <v>6914203</v>
+        <v>6914028</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,10 +2721,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134095337</v>
+        <v>134095261</v>
       </c>
       <c r="B21" t="n">
-        <v>91947</v>
+        <v>79390</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,21 +2732,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589774</v>
+        <v>589508</v>
       </c>
       <c r="R21" t="n">
-        <v>6914028</v>
+        <v>6914122</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2831,7 +2831,7 @@
         <v>134095265</v>
       </c>
       <c r="B22" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>134095335</v>
       </c>
       <c r="B23" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>134095350</v>
       </c>
       <c r="B24" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134095254</v>
+        <v>134095279</v>
       </c>
       <c r="B25" t="n">
-        <v>79380</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589525</v>
+        <v>589373</v>
       </c>
       <c r="R25" t="n">
-        <v>6914090</v>
+        <v>6914203</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3269,53 +3269,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134095359</v>
+        <v>134095254</v>
       </c>
       <c r="B26" t="n">
-        <v>57152</v>
+        <v>79390</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589567</v>
+        <v>589525</v>
       </c>
       <c r="R26" t="n">
-        <v>6914071</v>
+        <v>6914090</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3347,7 +3339,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3357,7 +3349,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,45 +3376,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134095336</v>
+        <v>134095359</v>
       </c>
       <c r="B27" t="n">
-        <v>91947</v>
+        <v>57162</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589761</v>
+        <v>589567</v>
       </c>
       <c r="R27" t="n">
-        <v>6914026</v>
+        <v>6914071</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3491,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134095279</v>
+        <v>134095292</v>
       </c>
       <c r="B28" t="n">
-        <v>91947</v>
+        <v>80473</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,21 +3502,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589373</v>
+        <v>589461</v>
       </c>
       <c r="R28" t="n">
-        <v>6914203</v>
+        <v>6914224</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3598,10 +3598,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134095292</v>
+        <v>134095336</v>
       </c>
       <c r="B29" t="n">
-        <v>80453</v>
+        <v>91957</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3609,21 +3609,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589461</v>
+        <v>589761</v>
       </c>
       <c r="R29" t="n">
-        <v>6914224</v>
+        <v>6914026</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,7 +3708,7 @@
         <v>134095294</v>
       </c>
       <c r="B30" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>134095323</v>
       </c>
       <c r="B31" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134095303</v>
+        <v>134095249</v>
       </c>
       <c r="B32" t="n">
-        <v>89328</v>
+        <v>79358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589501</v>
+        <v>589521</v>
       </c>
       <c r="R32" t="n">
-        <v>6914225</v>
+        <v>6914058</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4026,10 +4026,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134095249</v>
+        <v>134095287</v>
       </c>
       <c r="B33" t="n">
-        <v>79348</v>
+        <v>80473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589521</v>
+        <v>589437</v>
       </c>
       <c r="R33" t="n">
-        <v>6914058</v>
+        <v>6914217</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4133,10 +4133,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134095287</v>
+        <v>134095303</v>
       </c>
       <c r="B34" t="n">
-        <v>80453</v>
+        <v>89338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589437</v>
+        <v>589501</v>
       </c>
       <c r="R34" t="n">
-        <v>6914217</v>
+        <v>6914225</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4243,7 +4243,7 @@
         <v>134095330</v>
       </c>
       <c r="B35" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>134095258</v>
       </c>
       <c r="B36" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>134095349</v>
       </c>
       <c r="B37" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4574,45 +4574,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134095320</v>
+        <v>134095348</v>
       </c>
       <c r="B38" t="n">
-        <v>80481</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589619</v>
+        <v>589625</v>
       </c>
       <c r="R38" t="n">
-        <v>6914197</v>
+        <v>6914048</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4644,7 +4652,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4654,7 +4662,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4681,53 +4694,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134095348</v>
+        <v>134095320</v>
       </c>
       <c r="B39" t="n">
-        <v>57965</v>
+        <v>80477</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589625</v>
+        <v>589619</v>
       </c>
       <c r="R39" t="n">
-        <v>6914048</v>
+        <v>6914197</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4759,7 +4764,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4769,12 +4774,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4804,7 +4804,7 @@
         <v>134095341</v>
       </c>
       <c r="B40" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>134095308</v>
       </c>
       <c r="B41" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5015,32 +5015,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134095251</v>
+        <v>134095322</v>
       </c>
       <c r="B42" t="n">
-        <v>79348</v>
+        <v>80477</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5050,13 +5050,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589524</v>
+        <v>589690</v>
       </c>
       <c r="R42" t="n">
-        <v>6914076</v>
+        <v>6914189</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5122,10 +5122,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134095255</v>
+        <v>134095251</v>
       </c>
       <c r="B43" t="n">
-        <v>57965</v>
+        <v>79358</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5133,45 +5133,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589512</v>
+        <v>589524</v>
       </c>
       <c r="R43" t="n">
-        <v>6914087</v>
+        <v>6914076</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5200,7 +5192,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5210,12 +5202,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:08</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5242,45 +5229,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134095322</v>
+        <v>134095255</v>
       </c>
       <c r="B44" t="n">
-        <v>80481</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589690</v>
+        <v>589512</v>
       </c>
       <c r="R44" t="n">
-        <v>6914189</v>
+        <v>6914087</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5312,7 +5307,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5322,7 +5317,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5349,10 +5349,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134095280</v>
+        <v>134095311</v>
       </c>
       <c r="B45" t="n">
-        <v>92218</v>
+        <v>79358</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589373</v>
+        <v>589554</v>
       </c>
       <c r="R45" t="n">
-        <v>6914203</v>
+        <v>6914221</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5456,10 +5456,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134095311</v>
+        <v>134095316</v>
       </c>
       <c r="B46" t="n">
-        <v>79348</v>
+        <v>79390</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5467,21 +5467,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589554</v>
+        <v>589589</v>
       </c>
       <c r="R46" t="n">
-        <v>6914221</v>
+        <v>6914177</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5563,10 +5563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134095316</v>
+        <v>134095280</v>
       </c>
       <c r="B47" t="n">
-        <v>79380</v>
+        <v>92228</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5574,21 +5574,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589589</v>
+        <v>589373</v>
       </c>
       <c r="R47" t="n">
-        <v>6914177</v>
+        <v>6914203</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134095273</v>
+        <v>134095318</v>
       </c>
       <c r="B48" t="n">
-        <v>79380</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,34 +5681,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589415</v>
+        <v>589619</v>
       </c>
       <c r="R48" t="n">
-        <v>6914094</v>
+        <v>6914175</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5740,7 +5748,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5750,7 +5758,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5777,10 +5790,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134095326</v>
+        <v>134095264</v>
       </c>
       <c r="B49" t="n">
-        <v>79967</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,34 +5801,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589658</v>
+        <v>589558</v>
       </c>
       <c r="R49" t="n">
-        <v>6914134</v>
+        <v>6914160</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5847,7 +5868,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5857,7 +5878,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5887,7 +5913,7 @@
         <v>134095355</v>
       </c>
       <c r="B50" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5991,10 +6017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134095250</v>
+        <v>134095273</v>
       </c>
       <c r="B51" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6026,10 +6052,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589517</v>
+        <v>589415</v>
       </c>
       <c r="R51" t="n">
-        <v>6914061</v>
+        <v>6914094</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6061,7 +6087,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6071,7 +6097,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6098,10 +6124,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134095318</v>
+        <v>134095326</v>
       </c>
       <c r="B52" t="n">
-        <v>57965</v>
+        <v>79977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6109,42 +6135,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589619</v>
+        <v>589658</v>
       </c>
       <c r="R52" t="n">
-        <v>6914175</v>
+        <v>6914134</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6176,7 +6194,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6186,12 +6204,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6218,10 +6231,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134095264</v>
+        <v>134095250</v>
       </c>
       <c r="B53" t="n">
-        <v>57965</v>
+        <v>79390</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6229,42 +6242,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589558</v>
+        <v>589517</v>
       </c>
       <c r="R53" t="n">
-        <v>6914160</v>
+        <v>6914061</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6296,7 +6301,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6306,12 +6311,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6338,32 +6338,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134095353</v>
+        <v>134095296</v>
       </c>
       <c r="B54" t="n">
-        <v>79348</v>
+        <v>80423</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6373,10 +6373,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589598</v>
+        <v>589458</v>
       </c>
       <c r="R54" t="n">
-        <v>6914117</v>
+        <v>6914224</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6445,32 +6445,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134095296</v>
+        <v>134095277</v>
       </c>
       <c r="B55" t="n">
-        <v>80413</v>
+        <v>80336</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>392</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589458</v>
+        <v>589390</v>
       </c>
       <c r="R55" t="n">
-        <v>6914224</v>
+        <v>6914193</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6552,32 +6552,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134095277</v>
+        <v>134095272</v>
       </c>
       <c r="B56" t="n">
-        <v>80326</v>
+        <v>79390</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>392</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589390</v>
+        <v>589461</v>
       </c>
       <c r="R56" t="n">
-        <v>6914193</v>
+        <v>6914134</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6659,10 +6659,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134095272</v>
+        <v>134095353</v>
       </c>
       <c r="B57" t="n">
-        <v>79380</v>
+        <v>79358</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6670,21 +6670,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6694,10 +6694,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589461</v>
+        <v>589598</v>
       </c>
       <c r="R57" t="n">
-        <v>6914134</v>
+        <v>6914117</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6769,7 +6769,7 @@
         <v>134095345</v>
       </c>
       <c r="B58" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>134095304</v>
       </c>
       <c r="B59" t="n">
-        <v>83316</v>
+        <v>83326</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>134095339</v>
       </c>
       <c r="B60" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>134095356</v>
       </c>
       <c r="B61" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>134095344</v>
       </c>
       <c r="B62" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7314,32 +7314,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134095333</v>
+        <v>134095283</v>
       </c>
       <c r="B63" t="n">
-        <v>91958</v>
+        <v>79358</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589727</v>
+        <v>589376</v>
       </c>
       <c r="R63" t="n">
-        <v>6914106</v>
+        <v>6914228</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7421,10 +7421,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134095283</v>
+        <v>134095253</v>
       </c>
       <c r="B64" t="n">
-        <v>79348</v>
+        <v>79390</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7432,21 +7432,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>589376</v>
+        <v>589531</v>
       </c>
       <c r="R64" t="n">
-        <v>6914228</v>
+        <v>6914093</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7528,32 +7528,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134095253</v>
+        <v>134095333</v>
       </c>
       <c r="B65" t="n">
-        <v>79380</v>
+        <v>91968</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>1205</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7563,10 +7563,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>589531</v>
+        <v>589727</v>
       </c>
       <c r="R65" t="n">
-        <v>6914093</v>
+        <v>6914106</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7638,7 +7638,7 @@
         <v>134095310</v>
       </c>
       <c r="B66" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7742,32 +7742,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134095297</v>
+        <v>134095282</v>
       </c>
       <c r="B67" t="n">
-        <v>92126</v>
+        <v>89338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1503</v>
+        <v>510</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7777,10 +7777,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589461</v>
+        <v>589375</v>
       </c>
       <c r="R67" t="n">
-        <v>6914228</v>
+        <v>6914205</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7831,7 +7831,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7850,32 +7849,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134095271</v>
+        <v>134095297</v>
       </c>
       <c r="B68" t="n">
-        <v>79348</v>
+        <v>92136</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7885,10 +7884,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>589468</v>
+        <v>589461</v>
       </c>
       <c r="R68" t="n">
-        <v>6914148</v>
+        <v>6914228</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7920,7 +7919,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7930,7 +7929,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7939,6 +7938,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7957,10 +7957,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134095282</v>
+        <v>134095262</v>
       </c>
       <c r="B69" t="n">
-        <v>89328</v>
+        <v>79358</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7968,21 +7968,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>589375</v>
+        <v>589551</v>
       </c>
       <c r="R69" t="n">
-        <v>6914205</v>
+        <v>6914130</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8064,10 +8064,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134095262</v>
+        <v>134095271</v>
       </c>
       <c r="B70" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8099,10 +8099,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589551</v>
+        <v>589468</v>
       </c>
       <c r="R70" t="n">
-        <v>6914130</v>
+        <v>6914148</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8174,7 +8174,7 @@
         <v>134095275</v>
       </c>
       <c r="B71" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>134095288</v>
       </c>
       <c r="B72" t="n">
-        <v>91958</v>
+        <v>91968</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8385,10 +8385,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134095352</v>
+        <v>134095351</v>
       </c>
       <c r="B73" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>589608</v>
+        <v>589610</v>
       </c>
       <c r="R73" t="n">
-        <v>6914114</v>
+        <v>6914116</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8492,10 +8492,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134095351</v>
+        <v>134095286</v>
       </c>
       <c r="B74" t="n">
-        <v>91947</v>
+        <v>79358</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8503,21 +8503,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>589610</v>
+        <v>589414</v>
       </c>
       <c r="R74" t="n">
-        <v>6914116</v>
+        <v>6914214</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8599,10 +8599,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134095286</v>
+        <v>134095352</v>
       </c>
       <c r="B75" t="n">
-        <v>79348</v>
+        <v>91957</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8610,21 +8610,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8634,10 +8634,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>589414</v>
+        <v>589608</v>
       </c>
       <c r="R75" t="n">
-        <v>6914214</v>
+        <v>6914114</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8706,10 +8706,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134095343</v>
+        <v>134095274</v>
       </c>
       <c r="B76" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>589720</v>
+        <v>589385</v>
       </c>
       <c r="R76" t="n">
-        <v>6914011</v>
+        <v>6914116</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8813,10 +8813,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134095274</v>
+        <v>134095321</v>
       </c>
       <c r="B77" t="n">
-        <v>79380</v>
+        <v>57975</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8824,34 +8824,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>589385</v>
+        <v>589618</v>
       </c>
       <c r="R77" t="n">
-        <v>6914116</v>
+        <v>6914190</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8883,7 +8891,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8893,7 +8901,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8920,10 +8933,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134095321</v>
+        <v>134095319</v>
       </c>
       <c r="B78" t="n">
-        <v>57965</v>
+        <v>79390</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8931,42 +8944,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>589618</v>
+        <v>589626</v>
       </c>
       <c r="R78" t="n">
-        <v>6914190</v>
+        <v>6914176</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8998,7 +9003,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9008,12 +9013,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9040,10 +9040,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134095319</v>
+        <v>134095343</v>
       </c>
       <c r="B79" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9075,10 +9075,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589626</v>
+        <v>589720</v>
       </c>
       <c r="R79" t="n">
-        <v>6914176</v>
+        <v>6914011</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9150,7 +9150,7 @@
         <v>134095259</v>
       </c>
       <c r="B80" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>134095269</v>
       </c>
       <c r="B81" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>134095314</v>
       </c>
       <c r="B82" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>134095358</v>
       </c>
       <c r="B83" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>134095302</v>
       </c>
       <c r="B84" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>134095257</v>
       </c>
       <c r="B85" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9802,32 +9802,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134095307</v>
+        <v>134095342</v>
       </c>
       <c r="B86" t="n">
-        <v>80481</v>
+        <v>79390</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6461</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9837,10 +9837,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>589520</v>
+        <v>589787</v>
       </c>
       <c r="R86" t="n">
-        <v>6914195</v>
+        <v>6914002</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9909,32 +9909,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134095266</v>
+        <v>134095307</v>
       </c>
       <c r="B87" t="n">
-        <v>79380</v>
+        <v>80477</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>6461</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9944,10 +9944,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>589544</v>
+        <v>589520</v>
       </c>
       <c r="R87" t="n">
-        <v>6914176</v>
+        <v>6914195</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10016,10 +10016,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134095342</v>
+        <v>134095266</v>
       </c>
       <c r="B88" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>589787</v>
+        <v>589544</v>
       </c>
       <c r="R88" t="n">
-        <v>6914002</v>
+        <v>6914176</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10123,32 +10123,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134095267</v>
+        <v>134095263</v>
       </c>
       <c r="B89" t="n">
-        <v>79380</v>
+        <v>80367</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589498</v>
+        <v>589541</v>
       </c>
       <c r="R89" t="n">
-        <v>6914160</v>
+        <v>6914140</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10230,32 +10230,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134095263</v>
+        <v>134095267</v>
       </c>
       <c r="B90" t="n">
-        <v>80357</v>
+        <v>79390</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10265,10 +10265,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589541</v>
+        <v>589498</v>
       </c>
       <c r="R90" t="n">
-        <v>6914140</v>
+        <v>6914160</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10340,7 +10340,7 @@
         <v>134095317</v>
       </c>
       <c r="B91" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>134095328</v>
       </c>
       <c r="B92" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>134095340</v>
       </c>
       <c r="B93" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>134095331</v>
       </c>
       <c r="B94" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>134095329</v>
       </c>
       <c r="B95" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>134095312</v>
       </c>
       <c r="B96" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 59973-2025 artfynd.xlsx
+++ b/artfynd/A 59973-2025 artfynd.xlsx
@@ -1223,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134095305</v>
+        <v>134095313</v>
       </c>
       <c r="B7" t="n">
-        <v>80423</v>
+        <v>79390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589501</v>
+        <v>589577</v>
       </c>
       <c r="R7" t="n">
-        <v>6914218</v>
+        <v>6914208</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134095285</v>
+        <v>134095260</v>
       </c>
       <c r="B8" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589377</v>
+        <v>589507</v>
       </c>
       <c r="R8" t="n">
-        <v>6914229</v>
+        <v>6914122</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,32 +1437,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134095313</v>
+        <v>134095305</v>
       </c>
       <c r="B9" t="n">
-        <v>79390</v>
+        <v>80423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589577</v>
+        <v>589501</v>
       </c>
       <c r="R9" t="n">
-        <v>6914208</v>
+        <v>6914218</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134095260</v>
+        <v>134095285</v>
       </c>
       <c r="B10" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589507</v>
+        <v>589377</v>
       </c>
       <c r="R10" t="n">
-        <v>6914122</v>
+        <v>6914229</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1865,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134095346</v>
+        <v>134095289</v>
       </c>
       <c r="B13" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1876,21 +1876,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589671</v>
+        <v>589423</v>
       </c>
       <c r="R13" t="n">
-        <v>6914046</v>
+        <v>6914227</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134095289</v>
+        <v>134095291</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589423</v>
+        <v>589424</v>
       </c>
       <c r="R14" t="n">
-        <v>6914227</v>
+        <v>6914230</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134095291</v>
+        <v>134095346</v>
       </c>
       <c r="B15" t="n">
-        <v>91957</v>
+        <v>79390</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589424</v>
+        <v>589671</v>
       </c>
       <c r="R15" t="n">
-        <v>6914230</v>
+        <v>6914046</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,32 +2186,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134095324</v>
+        <v>134095309</v>
       </c>
       <c r="B16" t="n">
-        <v>79390</v>
+        <v>80423</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589658</v>
+        <v>589523</v>
       </c>
       <c r="R16" t="n">
-        <v>6914166</v>
+        <v>6914208</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,32 +2293,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134095309</v>
+        <v>134095281</v>
       </c>
       <c r="B17" t="n">
-        <v>80423</v>
+        <v>92389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589523</v>
+        <v>589375</v>
       </c>
       <c r="R17" t="n">
-        <v>6914208</v>
+        <v>6914203</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134095252</v>
+        <v>134095337</v>
       </c>
       <c r="B18" t="n">
-        <v>79390</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2411,21 +2411,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589531</v>
+        <v>589774</v>
       </c>
       <c r="R18" t="n">
-        <v>6914096</v>
+        <v>6914028</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,32 +2507,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134095281</v>
+        <v>134095261</v>
       </c>
       <c r="B19" t="n">
-        <v>92389</v>
+        <v>79390</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589375</v>
+        <v>589508</v>
       </c>
       <c r="R19" t="n">
-        <v>6914203</v>
+        <v>6914122</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2614,10 +2614,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134095337</v>
+        <v>134095265</v>
       </c>
       <c r="B20" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,34 +2625,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589774</v>
+        <v>589546</v>
       </c>
       <c r="R20" t="n">
-        <v>6914028</v>
+        <v>6914177</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2684,7 +2692,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2694,7 +2702,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,7 +2734,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134095261</v>
+        <v>134095324</v>
       </c>
       <c r="B21" t="n">
         <v>79390</v>
@@ -2756,10 +2769,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589508</v>
+        <v>589658</v>
       </c>
       <c r="R21" t="n">
-        <v>6914122</v>
+        <v>6914166</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2791,7 +2804,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2801,7 +2814,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2828,10 +2841,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134095265</v>
+        <v>134095252</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>79390</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,42 +2852,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589546</v>
+        <v>589531</v>
       </c>
       <c r="R22" t="n">
-        <v>6914177</v>
+        <v>6914096</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2906,7 +2911,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2916,12 +2921,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3162,45 +3162,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134095279</v>
+        <v>134095359</v>
       </c>
       <c r="B25" t="n">
-        <v>91957</v>
+        <v>57162</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589373</v>
+        <v>589567</v>
       </c>
       <c r="R25" t="n">
-        <v>6914203</v>
+        <v>6914071</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3232,7 +3240,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3242,7 +3250,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3269,10 +3277,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134095254</v>
+        <v>134095336</v>
       </c>
       <c r="B26" t="n">
-        <v>79390</v>
+        <v>91957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3280,21 +3288,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3304,10 +3312,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589525</v>
+        <v>589761</v>
       </c>
       <c r="R26" t="n">
-        <v>6914090</v>
+        <v>6914026</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3339,7 +3347,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3349,7 +3357,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3376,53 +3384,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134095359</v>
+        <v>134095279</v>
       </c>
       <c r="B27" t="n">
-        <v>57162</v>
+        <v>91957</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589567</v>
+        <v>589373</v>
       </c>
       <c r="R27" t="n">
-        <v>6914071</v>
+        <v>6914203</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3491,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134095292</v>
+        <v>134095254</v>
       </c>
       <c r="B28" t="n">
-        <v>80473</v>
+        <v>79390</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,21 +3502,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589461</v>
+        <v>589525</v>
       </c>
       <c r="R28" t="n">
-        <v>6914224</v>
+        <v>6914090</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3598,10 +3598,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134095336</v>
+        <v>134095292</v>
       </c>
       <c r="B29" t="n">
-        <v>91957</v>
+        <v>80473</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3609,21 +3609,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589761</v>
+        <v>589461</v>
       </c>
       <c r="R29" t="n">
-        <v>6914026</v>
+        <v>6914224</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,10 +3919,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134095249</v>
+        <v>134095303</v>
       </c>
       <c r="B32" t="n">
-        <v>79358</v>
+        <v>89338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589521</v>
+        <v>589501</v>
       </c>
       <c r="R32" t="n">
-        <v>6914058</v>
+        <v>6914225</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4026,10 +4026,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134095287</v>
+        <v>134095249</v>
       </c>
       <c r="B33" t="n">
-        <v>80473</v>
+        <v>79358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589437</v>
+        <v>589521</v>
       </c>
       <c r="R33" t="n">
-        <v>6914217</v>
+        <v>6914058</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4133,10 +4133,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134095303</v>
+        <v>134095287</v>
       </c>
       <c r="B34" t="n">
-        <v>89338</v>
+        <v>80473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589501</v>
+        <v>589437</v>
       </c>
       <c r="R34" t="n">
-        <v>6914225</v>
+        <v>6914217</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4347,10 +4347,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134095258</v>
+        <v>134095349</v>
       </c>
       <c r="B36" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,34 +4358,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589495</v>
+        <v>589619</v>
       </c>
       <c r="R36" t="n">
-        <v>6914097</v>
+        <v>6914055</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4417,7 +4425,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4427,7 +4435,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4454,10 +4467,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134095349</v>
+        <v>134095258</v>
       </c>
       <c r="B37" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4465,42 +4478,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589619</v>
+        <v>589495</v>
       </c>
       <c r="R37" t="n">
-        <v>6914055</v>
+        <v>6914097</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4532,7 +4537,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4542,12 +4547,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5122,10 +5122,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134095251</v>
+        <v>134095255</v>
       </c>
       <c r="B43" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5133,37 +5133,45 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589524</v>
+        <v>589512</v>
       </c>
       <c r="R43" t="n">
-        <v>6914076</v>
+        <v>6914087</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5192,7 +5200,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5202,7 +5210,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5229,10 +5242,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134095255</v>
+        <v>134095251</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5240,45 +5253,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589512</v>
+        <v>589524</v>
       </c>
       <c r="R44" t="n">
-        <v>6914087</v>
+        <v>6914076</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5307,7 +5312,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5317,12 +5322,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:08</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6017,10 +6017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134095273</v>
+        <v>134095326</v>
       </c>
       <c r="B51" t="n">
-        <v>79390</v>
+        <v>79977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6028,21 +6028,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589415</v>
+        <v>589658</v>
       </c>
       <c r="R51" t="n">
-        <v>6914094</v>
+        <v>6914134</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6124,10 +6124,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134095326</v>
+        <v>134095250</v>
       </c>
       <c r="B52" t="n">
-        <v>79977</v>
+        <v>79390</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6135,21 +6135,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589658</v>
+        <v>589517</v>
       </c>
       <c r="R52" t="n">
-        <v>6914134</v>
+        <v>6914061</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,7 +6231,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134095250</v>
+        <v>134095273</v>
       </c>
       <c r="B53" t="n">
         <v>79390</v>
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589517</v>
+        <v>589415</v>
       </c>
       <c r="R53" t="n">
-        <v>6914061</v>
+        <v>6914094</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6445,32 +6445,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134095277</v>
+        <v>134095353</v>
       </c>
       <c r="B55" t="n">
-        <v>80336</v>
+        <v>79358</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589390</v>
+        <v>589598</v>
       </c>
       <c r="R55" t="n">
-        <v>6914193</v>
+        <v>6914117</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6552,32 +6552,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134095272</v>
+        <v>134095277</v>
       </c>
       <c r="B56" t="n">
-        <v>79390</v>
+        <v>80336</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>392</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589461</v>
+        <v>589390</v>
       </c>
       <c r="R56" t="n">
-        <v>6914134</v>
+        <v>6914193</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6659,10 +6659,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134095353</v>
+        <v>134095272</v>
       </c>
       <c r="B57" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6670,21 +6670,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6694,10 +6694,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589598</v>
+        <v>589461</v>
       </c>
       <c r="R57" t="n">
-        <v>6914117</v>
+        <v>6914134</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6766,32 +6766,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134095345</v>
+        <v>134095304</v>
       </c>
       <c r="B58" t="n">
-        <v>79390</v>
+        <v>83326</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6439</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6801,13 +6801,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589680</v>
+        <v>589499</v>
       </c>
       <c r="R58" t="n">
-        <v>6914079</v>
+        <v>6914219</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6873,32 +6873,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134095304</v>
+        <v>134095345</v>
       </c>
       <c r="B59" t="n">
-        <v>83326</v>
+        <v>79390</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589499</v>
+        <v>589680</v>
       </c>
       <c r="R59" t="n">
-        <v>6914219</v>
+        <v>6914079</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7957,10 +7957,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134095262</v>
+        <v>134095275</v>
       </c>
       <c r="B69" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7968,21 +7968,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>589551</v>
+        <v>589368</v>
       </c>
       <c r="R69" t="n">
-        <v>6914130</v>
+        <v>6914134</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8064,7 +8064,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134095271</v>
+        <v>134095262</v>
       </c>
       <c r="B70" t="n">
         <v>79358</v>
@@ -8099,10 +8099,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589468</v>
+        <v>589551</v>
       </c>
       <c r="R70" t="n">
-        <v>6914148</v>
+        <v>6914130</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8171,10 +8171,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134095275</v>
+        <v>134095271</v>
       </c>
       <c r="B71" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8182,21 +8182,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>589368</v>
+        <v>589468</v>
       </c>
       <c r="R71" t="n">
-        <v>6914134</v>
+        <v>6914148</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9040,10 +9040,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134095343</v>
+        <v>134095259</v>
       </c>
       <c r="B79" t="n">
-        <v>79390</v>
+        <v>89338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9051,21 +9051,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9075,10 +9075,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589720</v>
+        <v>589496</v>
       </c>
       <c r="R79" t="n">
-        <v>6914011</v>
+        <v>6914098</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9147,10 +9147,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134095259</v>
+        <v>134095343</v>
       </c>
       <c r="B80" t="n">
-        <v>89338</v>
+        <v>79390</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9158,21 +9158,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9182,10 +9182,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589496</v>
+        <v>589720</v>
       </c>
       <c r="R80" t="n">
-        <v>6914098</v>
+        <v>6914011</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10123,32 +10123,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134095263</v>
+        <v>134095267</v>
       </c>
       <c r="B89" t="n">
-        <v>80367</v>
+        <v>79390</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589541</v>
+        <v>589498</v>
       </c>
       <c r="R89" t="n">
-        <v>6914140</v>
+        <v>6914160</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10230,10 +10230,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134095267</v>
+        <v>134095317</v>
       </c>
       <c r="B90" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10241,21 +10241,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10265,10 +10265,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>589498</v>
+        <v>589590</v>
       </c>
       <c r="R90" t="n">
-        <v>6914160</v>
+        <v>6914172</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10337,32 +10337,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134095317</v>
+        <v>134095263</v>
       </c>
       <c r="B91" t="n">
-        <v>79358</v>
+        <v>80367</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10372,10 +10372,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>589590</v>
+        <v>589541</v>
       </c>
       <c r="R91" t="n">
-        <v>6914172</v>
+        <v>6914140</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 59973-2025 artfynd.xlsx
+++ b/artfynd/A 59973-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134095278</v>
+        <v>134095306</v>
       </c>
       <c r="B2" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589380</v>
+        <v>589505</v>
       </c>
       <c r="R2" t="n">
         <v>6914198</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +795,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134095276</v>
+        <v>134095299</v>
       </c>
       <c r="B3" t="n">
-        <v>79390</v>
+        <v>80423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589351</v>
+        <v>589504</v>
       </c>
       <c r="R3" t="n">
-        <v>6914144</v>
+        <v>6914263</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134095306</v>
+        <v>134095278</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +913,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589505</v>
+        <v>589380</v>
       </c>
       <c r="R4" t="n">
         <v>6914198</v>
@@ -967,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,12 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,32 +1009,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134095299</v>
+        <v>134095276</v>
       </c>
       <c r="B5" t="n">
-        <v>80423</v>
+        <v>79390</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589504</v>
+        <v>589351</v>
       </c>
       <c r="R5" t="n">
-        <v>6914263</v>
+        <v>6914144</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,32 +1116,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134095248</v>
+        <v>134095305</v>
       </c>
       <c r="B6" t="n">
-        <v>79390</v>
+        <v>80423</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589533</v>
+        <v>589501</v>
       </c>
       <c r="R6" t="n">
-        <v>6914053</v>
+        <v>6914218</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1223,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134095313</v>
+        <v>134095285</v>
       </c>
       <c r="B7" t="n">
         <v>79390</v>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589577</v>
+        <v>589377</v>
       </c>
       <c r="R7" t="n">
-        <v>6914208</v>
+        <v>6914229</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134095260</v>
+        <v>134095313</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589507</v>
+        <v>589577</v>
       </c>
       <c r="R8" t="n">
-        <v>6914122</v>
+        <v>6914208</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,32 +1437,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134095305</v>
+        <v>134095260</v>
       </c>
       <c r="B9" t="n">
-        <v>80423</v>
+        <v>79358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589501</v>
+        <v>589507</v>
       </c>
       <c r="R9" t="n">
-        <v>6914218</v>
+        <v>6914122</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,7 +1544,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134095285</v>
+        <v>134095248</v>
       </c>
       <c r="B10" t="n">
         <v>79390</v>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589377</v>
+        <v>589533</v>
       </c>
       <c r="R10" t="n">
-        <v>6914229</v>
+        <v>6914053</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,32 +1651,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134095270</v>
+        <v>134095346</v>
       </c>
       <c r="B11" t="n">
-        <v>91920</v>
+        <v>79390</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589483</v>
+        <v>589671</v>
       </c>
       <c r="R11" t="n">
-        <v>6914142</v>
+        <v>6914046</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134095293</v>
+        <v>134095270</v>
       </c>
       <c r="B12" t="n">
-        <v>80423</v>
+        <v>91920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589461</v>
+        <v>589483</v>
       </c>
       <c r="R12" t="n">
-        <v>6914225</v>
+        <v>6914142</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,32 +1865,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134095289</v>
+        <v>134095293</v>
       </c>
       <c r="B13" t="n">
-        <v>79358</v>
+        <v>80423</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589423</v>
+        <v>589461</v>
       </c>
       <c r="R13" t="n">
-        <v>6914227</v>
+        <v>6914225</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134095346</v>
+        <v>134095289</v>
       </c>
       <c r="B15" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589671</v>
+        <v>589423</v>
       </c>
       <c r="R15" t="n">
-        <v>6914046</v>
+        <v>6914227</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,32 +2293,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134095281</v>
+        <v>134095324</v>
       </c>
       <c r="B17" t="n">
-        <v>92389</v>
+        <v>79390</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589375</v>
+        <v>589658</v>
       </c>
       <c r="R17" t="n">
-        <v>6914203</v>
+        <v>6914166</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134095337</v>
+        <v>134095252</v>
       </c>
       <c r="B18" t="n">
-        <v>91957</v>
+        <v>79390</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2411,21 +2411,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589774</v>
+        <v>589531</v>
       </c>
       <c r="R18" t="n">
-        <v>6914028</v>
+        <v>6914096</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,32 +2507,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134095261</v>
+        <v>134095281</v>
       </c>
       <c r="B19" t="n">
-        <v>79390</v>
+        <v>92389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589508</v>
+        <v>589375</v>
       </c>
       <c r="R19" t="n">
-        <v>6914122</v>
+        <v>6914203</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2614,10 +2614,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134095265</v>
+        <v>134095337</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,42 +2625,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589546</v>
+        <v>589774</v>
       </c>
       <c r="R20" t="n">
-        <v>6914177</v>
+        <v>6914028</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2692,7 +2684,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2702,12 +2694,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2734,7 +2721,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134095324</v>
+        <v>134095261</v>
       </c>
       <c r="B21" t="n">
         <v>79390</v>
@@ -2769,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589658</v>
+        <v>589508</v>
       </c>
       <c r="R21" t="n">
-        <v>6914166</v>
+        <v>6914122</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2804,7 +2791,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2814,7 +2801,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2841,10 +2828,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134095252</v>
+        <v>134095265</v>
       </c>
       <c r="B22" t="n">
-        <v>79390</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2852,34 +2839,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589531</v>
+        <v>589546</v>
       </c>
       <c r="R22" t="n">
-        <v>6914096</v>
+        <v>6914177</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2911,7 +2906,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2921,7 +2916,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3162,56 +3162,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134095359</v>
+        <v>134095294</v>
       </c>
       <c r="B25" t="n">
-        <v>57162</v>
+        <v>80473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589567</v>
+        <v>589458</v>
       </c>
       <c r="R25" t="n">
-        <v>6914071</v>
+        <v>6914224</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3240,7 +3232,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3250,7 +3242,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,7 +3269,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134095336</v>
+        <v>134095279</v>
       </c>
       <c r="B26" t="n">
         <v>91957</v>
@@ -3312,10 +3304,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589761</v>
+        <v>589373</v>
       </c>
       <c r="R26" t="n">
-        <v>6914026</v>
+        <v>6914203</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3347,7 +3339,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3357,7 +3349,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134095279</v>
+        <v>134095254</v>
       </c>
       <c r="B27" t="n">
-        <v>91957</v>
+        <v>79390</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3395,21 +3387,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3419,10 +3411,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589373</v>
+        <v>589525</v>
       </c>
       <c r="R27" t="n">
-        <v>6914203</v>
+        <v>6914090</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3454,7 +3446,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3464,7 +3456,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3491,45 +3483,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134095254</v>
+        <v>134095359</v>
       </c>
       <c r="B28" t="n">
-        <v>79390</v>
+        <v>57162</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589525</v>
+        <v>589567</v>
       </c>
       <c r="R28" t="n">
-        <v>6914090</v>
+        <v>6914071</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134095294</v>
+        <v>134095336</v>
       </c>
       <c r="B30" t="n">
-        <v>80473</v>
+        <v>91957</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589458</v>
+        <v>589761</v>
       </c>
       <c r="R30" t="n">
-        <v>6914224</v>
+        <v>6914026</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3919,10 +3919,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134095303</v>
+        <v>134095249</v>
       </c>
       <c r="B32" t="n">
-        <v>89338</v>
+        <v>79358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589501</v>
+        <v>589521</v>
       </c>
       <c r="R32" t="n">
-        <v>6914225</v>
+        <v>6914058</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4026,10 +4026,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134095249</v>
+        <v>134095287</v>
       </c>
       <c r="B33" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589521</v>
+        <v>589437</v>
       </c>
       <c r="R33" t="n">
-        <v>6914058</v>
+        <v>6914217</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4133,10 +4133,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134095287</v>
+        <v>134095303</v>
       </c>
       <c r="B34" t="n">
-        <v>80473</v>
+        <v>89338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589437</v>
+        <v>589501</v>
       </c>
       <c r="R34" t="n">
-        <v>6914217</v>
+        <v>6914225</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4347,10 +4347,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134095349</v>
+        <v>134095258</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,42 +4358,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589619</v>
+        <v>589495</v>
       </c>
       <c r="R36" t="n">
-        <v>6914055</v>
+        <v>6914097</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4425,7 +4417,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4435,12 +4427,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4467,10 +4454,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134095258</v>
+        <v>134095349</v>
       </c>
       <c r="B37" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4478,34 +4465,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589495</v>
+        <v>589619</v>
       </c>
       <c r="R37" t="n">
-        <v>6914097</v>
+        <v>6914055</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4537,7 +4532,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4547,7 +4542,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4574,53 +4574,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134095348</v>
+        <v>134095320</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>80477</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589625</v>
+        <v>589619</v>
       </c>
       <c r="R38" t="n">
-        <v>6914048</v>
+        <v>6914197</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4652,7 +4644,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4662,12 +4654,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4694,45 +4681,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134095320</v>
+        <v>134095348</v>
       </c>
       <c r="B39" t="n">
-        <v>80477</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589619</v>
+        <v>589625</v>
       </c>
       <c r="R39" t="n">
-        <v>6914197</v>
+        <v>6914048</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4764,7 +4759,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4774,7 +4769,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4908,32 +4908,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134095308</v>
+        <v>134095322</v>
       </c>
       <c r="B41" t="n">
-        <v>79358</v>
+        <v>80477</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589516</v>
+        <v>589690</v>
       </c>
       <c r="R41" t="n">
-        <v>6914199</v>
+        <v>6914189</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5015,32 +5015,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134095322</v>
+        <v>134095308</v>
       </c>
       <c r="B42" t="n">
-        <v>80477</v>
+        <v>79358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5050,13 +5050,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589690</v>
+        <v>589516</v>
       </c>
       <c r="R42" t="n">
-        <v>6914189</v>
+        <v>6914199</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5122,10 +5122,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134095255</v>
+        <v>134095251</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5133,45 +5133,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589512</v>
+        <v>589524</v>
       </c>
       <c r="R43" t="n">
-        <v>6914087</v>
+        <v>6914076</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5200,7 +5192,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5210,12 +5202,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:08</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5242,10 +5229,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134095251</v>
+        <v>134095255</v>
       </c>
       <c r="B44" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5253,37 +5240,45 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589524</v>
+        <v>589512</v>
       </c>
       <c r="R44" t="n">
-        <v>6914076</v>
+        <v>6914087</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5312,7 +5307,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5322,7 +5317,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5349,10 +5349,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134095311</v>
+        <v>134095316</v>
       </c>
       <c r="B45" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589554</v>
+        <v>589589</v>
       </c>
       <c r="R45" t="n">
-        <v>6914221</v>
+        <v>6914177</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5456,10 +5456,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134095316</v>
+        <v>134095311</v>
       </c>
       <c r="B46" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5467,21 +5467,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589589</v>
+        <v>589554</v>
       </c>
       <c r="R46" t="n">
-        <v>6914177</v>
+        <v>6914221</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134095318</v>
+        <v>134095326</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>79977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,42 +5681,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589619</v>
+        <v>589658</v>
       </c>
       <c r="R48" t="n">
-        <v>6914175</v>
+        <v>6914134</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5748,7 +5740,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5758,12 +5750,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5790,10 +5777,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134095264</v>
+        <v>134095250</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>79390</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5801,42 +5788,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589558</v>
+        <v>589517</v>
       </c>
       <c r="R49" t="n">
-        <v>6914160</v>
+        <v>6914061</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5868,7 +5847,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5878,12 +5857,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5910,10 +5884,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134095355</v>
+        <v>134095318</v>
       </c>
       <c r="B50" t="n">
-        <v>79390</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5921,34 +5895,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589591</v>
+        <v>589619</v>
       </c>
       <c r="R50" t="n">
-        <v>6914124</v>
+        <v>6914175</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5980,7 +5962,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5990,7 +5972,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6017,10 +6004,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134095326</v>
+        <v>134095264</v>
       </c>
       <c r="B51" t="n">
-        <v>79977</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6028,34 +6015,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589658</v>
+        <v>589558</v>
       </c>
       <c r="R51" t="n">
-        <v>6914134</v>
+        <v>6914160</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6087,7 +6082,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6097,7 +6092,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6124,7 +6124,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134095250</v>
+        <v>134095355</v>
       </c>
       <c r="B52" t="n">
         <v>79390</v>
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589517</v>
+        <v>589591</v>
       </c>
       <c r="R52" t="n">
-        <v>6914061</v>
+        <v>6914124</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6338,32 +6338,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134095296</v>
+        <v>134095272</v>
       </c>
       <c r="B54" t="n">
-        <v>80423</v>
+        <v>79390</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6373,10 +6373,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589458</v>
+        <v>589461</v>
       </c>
       <c r="R54" t="n">
-        <v>6914224</v>
+        <v>6914134</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6445,32 +6445,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134095353</v>
+        <v>134095296</v>
       </c>
       <c r="B55" t="n">
-        <v>79358</v>
+        <v>80423</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589598</v>
+        <v>589458</v>
       </c>
       <c r="R55" t="n">
-        <v>6914117</v>
+        <v>6914224</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6659,10 +6659,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134095272</v>
+        <v>134095353</v>
       </c>
       <c r="B57" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6670,21 +6670,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6694,10 +6694,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589461</v>
+        <v>589598</v>
       </c>
       <c r="R57" t="n">
-        <v>6914134</v>
+        <v>6914117</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6766,32 +6766,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134095304</v>
+        <v>134095339</v>
       </c>
       <c r="B58" t="n">
-        <v>83326</v>
+        <v>79390</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6801,13 +6801,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589499</v>
+        <v>589780</v>
       </c>
       <c r="R58" t="n">
-        <v>6914219</v>
+        <v>6914027</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6980,32 +6980,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134095339</v>
+        <v>134095304</v>
       </c>
       <c r="B60" t="n">
-        <v>79390</v>
+        <v>83326</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6439</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589780</v>
+        <v>589499</v>
       </c>
       <c r="R60" t="n">
-        <v>6914027</v>
+        <v>6914219</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7314,10 +7314,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134095283</v>
+        <v>134095253</v>
       </c>
       <c r="B63" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7325,21 +7325,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>589376</v>
+        <v>589531</v>
       </c>
       <c r="R63" t="n">
-        <v>6914228</v>
+        <v>6914093</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7421,32 +7421,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134095253</v>
+        <v>134095333</v>
       </c>
       <c r="B64" t="n">
-        <v>79390</v>
+        <v>91968</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>1205</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>589531</v>
+        <v>589727</v>
       </c>
       <c r="R64" t="n">
-        <v>6914093</v>
+        <v>6914106</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7528,32 +7528,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134095333</v>
+        <v>134095310</v>
       </c>
       <c r="B65" t="n">
-        <v>91968</v>
+        <v>83343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1205</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7563,10 +7563,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>589727</v>
+        <v>589530</v>
       </c>
       <c r="R65" t="n">
-        <v>6914106</v>
+        <v>6914215</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7635,10 +7635,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134095310</v>
+        <v>134095283</v>
       </c>
       <c r="B66" t="n">
-        <v>83343</v>
+        <v>79358</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7646,21 +7646,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>589530</v>
+        <v>589376</v>
       </c>
       <c r="R66" t="n">
-        <v>6914215</v>
+        <v>6914228</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7742,32 +7742,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134095282</v>
+        <v>134095297</v>
       </c>
       <c r="B67" t="n">
-        <v>89338</v>
+        <v>92136</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>510</v>
+        <v>1503</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7777,10 +7777,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>589375</v>
+        <v>589461</v>
       </c>
       <c r="R67" t="n">
-        <v>6914205</v>
+        <v>6914228</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7831,6 +7831,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7849,32 +7850,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134095297</v>
+        <v>134095262</v>
       </c>
       <c r="B68" t="n">
-        <v>92136</v>
+        <v>79358</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7884,10 +7885,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>589461</v>
+        <v>589551</v>
       </c>
       <c r="R68" t="n">
-        <v>6914228</v>
+        <v>6914130</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7919,7 +7920,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7929,7 +7930,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7938,7 +7939,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8064,10 +8064,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134095262</v>
+        <v>134095282</v>
       </c>
       <c r="B70" t="n">
-        <v>79358</v>
+        <v>89338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8075,21 +8075,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8099,10 +8099,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>589551</v>
+        <v>589375</v>
       </c>
       <c r="R70" t="n">
-        <v>6914130</v>
+        <v>6914205</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8933,7 +8933,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134095319</v>
+        <v>134095343</v>
       </c>
       <c r="B78" t="n">
         <v>79390</v>
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>589626</v>
+        <v>589720</v>
       </c>
       <c r="R78" t="n">
-        <v>6914176</v>
+        <v>6914011</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9040,10 +9040,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134095259</v>
+        <v>134095269</v>
       </c>
       <c r="B79" t="n">
-        <v>89338</v>
+        <v>79358</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9051,21 +9051,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9075,10 +9075,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>589496</v>
+        <v>589498</v>
       </c>
       <c r="R79" t="n">
-        <v>6914098</v>
+        <v>6914160</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9147,7 +9147,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134095343</v>
+        <v>134095314</v>
       </c>
       <c r="B80" t="n">
         <v>79390</v>
@@ -9182,10 +9182,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>589720</v>
+        <v>589578</v>
       </c>
       <c r="R80" t="n">
-        <v>6914011</v>
+        <v>6914200</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9254,10 +9254,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134095269</v>
+        <v>134095319</v>
       </c>
       <c r="B81" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9265,21 +9265,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9289,10 +9289,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>589498</v>
+        <v>589626</v>
       </c>
       <c r="R81" t="n">
-        <v>6914160</v>
+        <v>6914176</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9361,10 +9361,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134095314</v>
+        <v>134095259</v>
       </c>
       <c r="B82" t="n">
-        <v>79390</v>
+        <v>89338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9372,21 +9372,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9396,10 +9396,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>589578</v>
+        <v>589496</v>
       </c>
       <c r="R82" t="n">
-        <v>6914200</v>
+        <v>6914098</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9468,10 +9468,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134095358</v>
+        <v>134095302</v>
       </c>
       <c r="B83" t="n">
-        <v>57975</v>
+        <v>80473</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9479,42 +9479,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>589566</v>
+        <v>589510</v>
       </c>
       <c r="R83" t="n">
-        <v>6914072</v>
+        <v>6914242</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9546,7 +9538,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9556,12 +9548,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9588,10 +9575,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134095302</v>
+        <v>134095342</v>
       </c>
       <c r="B84" t="n">
-        <v>80473</v>
+        <v>79390</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9599,21 +9586,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9623,10 +9610,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>589510</v>
+        <v>589787</v>
       </c>
       <c r="R84" t="n">
-        <v>6914242</v>
+        <v>6914002</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9658,7 +9645,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9668,7 +9655,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9695,32 +9682,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134095257</v>
+        <v>134095307</v>
       </c>
       <c r="B85" t="n">
-        <v>79390</v>
+        <v>80477</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6461</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9730,10 +9717,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>589500</v>
+        <v>589520</v>
       </c>
       <c r="R85" t="n">
-        <v>6914077</v>
+        <v>6914195</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9765,7 +9752,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9775,7 +9762,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9802,7 +9789,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134095342</v>
+        <v>134095266</v>
       </c>
       <c r="B86" t="n">
         <v>79390</v>
@@ -9837,10 +9824,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>589787</v>
+        <v>589544</v>
       </c>
       <c r="R86" t="n">
-        <v>6914002</v>
+        <v>6914176</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9872,7 +9859,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9882,7 +9869,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9909,45 +9896,53 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134095307</v>
+        <v>134095358</v>
       </c>
       <c r="B87" t="n">
-        <v>80477</v>
+        <v>57975</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>589520</v>
+        <v>589566</v>
       </c>
       <c r="R87" t="n">
-        <v>6914195</v>
+        <v>6914072</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9979,7 +9974,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9989,7 +9984,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10016,7 +10016,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134095266</v>
+        <v>134095257</v>
       </c>
       <c r="B88" t="n">
         <v>79390</v>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>589544</v>
+        <v>589500</v>
       </c>
       <c r="R88" t="n">
-        <v>6914176</v>
+        <v>6914077</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10123,32 +10123,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134095267</v>
+        <v>134095263</v>
       </c>
       <c r="B89" t="n">
-        <v>79390</v>
+        <v>80367</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10158,10 +10158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>589498</v>
+        <v>589541</v>
       </c>
       <c r="R89" t="n">
-        <v>6914160</v>
+        <v>6914140</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10337,32 +10337,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134095263</v>
+        <v>134095267</v>
       </c>
       <c r="B91" t="n">
-        <v>80367</v>
+        <v>79390</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10372,10 +10372,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>589541</v>
+        <v>589498</v>
       </c>
       <c r="R91" t="n">
-        <v>6914140</v>
+        <v>6914160</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 59973-2025 artfynd.xlsx
+++ b/artfynd/A 59973-2025 artfynd.xlsx
@@ -3162,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134095294</v>
+        <v>134095279</v>
       </c>
       <c r="B25" t="n">
-        <v>80473</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589458</v>
+        <v>589373</v>
       </c>
       <c r="R25" t="n">
-        <v>6914224</v>
+        <v>6914203</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3269,10 +3269,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134095279</v>
+        <v>134095254</v>
       </c>
       <c r="B26" t="n">
-        <v>91957</v>
+        <v>79390</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3280,21 +3280,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589373</v>
+        <v>589525</v>
       </c>
       <c r="R26" t="n">
-        <v>6914203</v>
+        <v>6914090</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3376,45 +3376,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134095254</v>
+        <v>134095359</v>
       </c>
       <c r="B27" t="n">
-        <v>79390</v>
+        <v>57162</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589525</v>
+        <v>589567</v>
       </c>
       <c r="R27" t="n">
-        <v>6914090</v>
+        <v>6914071</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3446,7 +3454,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3456,7 +3464,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3483,53 +3491,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134095359</v>
+        <v>134095292</v>
       </c>
       <c r="B28" t="n">
-        <v>57162</v>
+        <v>80473</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589567</v>
+        <v>589461</v>
       </c>
       <c r="R28" t="n">
-        <v>6914071</v>
+        <v>6914224</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3598,10 +3598,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134095292</v>
+        <v>134095336</v>
       </c>
       <c r="B29" t="n">
-        <v>80473</v>
+        <v>91957</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3609,21 +3609,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589461</v>
+        <v>589761</v>
       </c>
       <c r="R29" t="n">
-        <v>6914224</v>
+        <v>6914026</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134095336</v>
+        <v>134095323</v>
       </c>
       <c r="B30" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589761</v>
+        <v>589690</v>
       </c>
       <c r="R30" t="n">
-        <v>6914026</v>
+        <v>6914184</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3812,10 +3812,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134095323</v>
+        <v>134095294</v>
       </c>
       <c r="B31" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589690</v>
+        <v>589458</v>
       </c>
       <c r="R31" t="n">
-        <v>6914184</v>
+        <v>6914224</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -6338,32 +6338,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134095272</v>
+        <v>134095296</v>
       </c>
       <c r="B54" t="n">
-        <v>79390</v>
+        <v>80423</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6373,10 +6373,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589461</v>
+        <v>589458</v>
       </c>
       <c r="R54" t="n">
-        <v>6914134</v>
+        <v>6914224</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6445,32 +6445,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134095296</v>
+        <v>134095277</v>
       </c>
       <c r="B55" t="n">
-        <v>80423</v>
+        <v>80336</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>392</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589458</v>
+        <v>589390</v>
       </c>
       <c r="R55" t="n">
-        <v>6914224</v>
+        <v>6914193</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6552,32 +6552,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134095277</v>
+        <v>134095353</v>
       </c>
       <c r="B56" t="n">
-        <v>80336</v>
+        <v>79358</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589390</v>
+        <v>589598</v>
       </c>
       <c r="R56" t="n">
-        <v>6914193</v>
+        <v>6914117</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6659,10 +6659,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134095353</v>
+        <v>134095272</v>
       </c>
       <c r="B57" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6670,21 +6670,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6694,10 +6694,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589598</v>
+        <v>589461</v>
       </c>
       <c r="R57" t="n">
-        <v>6914117</v>
+        <v>6914134</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 59973-2025 artfynd.xlsx
+++ b/artfynd/A 59973-2025 artfynd.xlsx
@@ -1758,32 +1758,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134095270</v>
+        <v>134095289</v>
       </c>
       <c r="B12" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589483</v>
+        <v>589423</v>
       </c>
       <c r="R12" t="n">
-        <v>6914142</v>
+        <v>6914227</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134095293</v>
+        <v>134095270</v>
       </c>
       <c r="B13" t="n">
-        <v>80423</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1876,21 +1876,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589461</v>
+        <v>589483</v>
       </c>
       <c r="R13" t="n">
-        <v>6914225</v>
+        <v>6914142</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,32 +1972,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134095291</v>
+        <v>134095293</v>
       </c>
       <c r="B14" t="n">
-        <v>91957</v>
+        <v>80423</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589424</v>
+        <v>589461</v>
       </c>
       <c r="R14" t="n">
-        <v>6914230</v>
+        <v>6914225</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134095289</v>
+        <v>134095291</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589423</v>
+        <v>589424</v>
       </c>
       <c r="R15" t="n">
-        <v>6914227</v>
+        <v>6914230</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3162,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134095279</v>
+        <v>134095294</v>
       </c>
       <c r="B25" t="n">
-        <v>91957</v>
+        <v>80473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589373</v>
+        <v>589458</v>
       </c>
       <c r="R25" t="n">
-        <v>6914203</v>
+        <v>6914224</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3269,10 +3269,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134095254</v>
+        <v>134095279</v>
       </c>
       <c r="B26" t="n">
-        <v>79390</v>
+        <v>91957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3280,21 +3280,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589525</v>
+        <v>589373</v>
       </c>
       <c r="R26" t="n">
-        <v>6914090</v>
+        <v>6914203</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3376,53 +3376,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134095359</v>
+        <v>134095254</v>
       </c>
       <c r="B27" t="n">
-        <v>57162</v>
+        <v>79390</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589567</v>
+        <v>589525</v>
       </c>
       <c r="R27" t="n">
-        <v>6914071</v>
+        <v>6914090</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3454,7 +3446,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3464,7 +3456,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3491,45 +3483,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134095292</v>
+        <v>134095359</v>
       </c>
       <c r="B28" t="n">
-        <v>80473</v>
+        <v>57162</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589461</v>
+        <v>589567</v>
       </c>
       <c r="R28" t="n">
-        <v>6914224</v>
+        <v>6914071</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3598,10 +3598,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134095336</v>
+        <v>134095292</v>
       </c>
       <c r="B29" t="n">
-        <v>91957</v>
+        <v>80473</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3609,21 +3609,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589761</v>
+        <v>589461</v>
       </c>
       <c r="R29" t="n">
-        <v>6914026</v>
+        <v>6914224</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3705,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134095323</v>
+        <v>134095336</v>
       </c>
       <c r="B30" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3716,21 +3716,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589690</v>
+        <v>589761</v>
       </c>
       <c r="R30" t="n">
-        <v>6914184</v>
+        <v>6914026</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3812,10 +3812,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134095294</v>
+        <v>134095323</v>
       </c>
       <c r="B31" t="n">
-        <v>80473</v>
+        <v>79358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589458</v>
+        <v>589690</v>
       </c>
       <c r="R31" t="n">
-        <v>6914224</v>
+        <v>6914184</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5349,10 +5349,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134095316</v>
+        <v>134095311</v>
       </c>
       <c r="B45" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589589</v>
+        <v>589554</v>
       </c>
       <c r="R45" t="n">
-        <v>6914177</v>
+        <v>6914221</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5456,10 +5456,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134095311</v>
+        <v>134095280</v>
       </c>
       <c r="B46" t="n">
-        <v>79358</v>
+        <v>92228</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5467,21 +5467,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589554</v>
+        <v>589373</v>
       </c>
       <c r="R46" t="n">
-        <v>6914221</v>
+        <v>6914203</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5563,10 +5563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134095280</v>
+        <v>134095316</v>
       </c>
       <c r="B47" t="n">
-        <v>92228</v>
+        <v>79390</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5574,21 +5574,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589373</v>
+        <v>589589</v>
       </c>
       <c r="R47" t="n">
-        <v>6914203</v>
+        <v>6914177</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134095326</v>
+        <v>134095318</v>
       </c>
       <c r="B48" t="n">
-        <v>79977</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,34 +5681,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589658</v>
+        <v>589619</v>
       </c>
       <c r="R48" t="n">
-        <v>6914134</v>
+        <v>6914175</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5740,7 +5748,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5750,7 +5758,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5777,10 +5790,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134095250</v>
+        <v>134095264</v>
       </c>
       <c r="B49" t="n">
-        <v>79390</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,34 +5801,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589517</v>
+        <v>589558</v>
       </c>
       <c r="R49" t="n">
-        <v>6914061</v>
+        <v>6914160</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5847,7 +5868,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5857,7 +5878,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5884,10 +5910,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134095318</v>
+        <v>134095355</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>79390</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5895,42 +5921,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589619</v>
+        <v>589591</v>
       </c>
       <c r="R50" t="n">
-        <v>6914175</v>
+        <v>6914124</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5962,7 +5980,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5972,12 +5990,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6004,10 +6017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134095264</v>
+        <v>134095273</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>79390</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6015,42 +6028,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589558</v>
+        <v>589415</v>
       </c>
       <c r="R51" t="n">
-        <v>6914160</v>
+        <v>6914094</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6082,7 +6087,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6092,12 +6097,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6124,10 +6124,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134095355</v>
+        <v>134095326</v>
       </c>
       <c r="B52" t="n">
-        <v>79390</v>
+        <v>79977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6135,21 +6135,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589591</v>
+        <v>589658</v>
       </c>
       <c r="R52" t="n">
-        <v>6914124</v>
+        <v>6914134</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,7 +6231,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134095273</v>
+        <v>134095250</v>
       </c>
       <c r="B53" t="n">
         <v>79390</v>
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589415</v>
+        <v>589517</v>
       </c>
       <c r="R53" t="n">
-        <v>6914094</v>
+        <v>6914061</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 59973-2025 artfynd.xlsx
+++ b/artfynd/A 59973-2025 artfynd.xlsx
@@ -5349,10 +5349,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134095311</v>
+        <v>134095316</v>
       </c>
       <c r="B45" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589554</v>
+        <v>589589</v>
       </c>
       <c r="R45" t="n">
-        <v>6914221</v>
+        <v>6914177</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5456,10 +5456,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134095280</v>
+        <v>134095311</v>
       </c>
       <c r="B46" t="n">
-        <v>92228</v>
+        <v>79358</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5467,21 +5467,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589373</v>
+        <v>589554</v>
       </c>
       <c r="R46" t="n">
-        <v>6914203</v>
+        <v>6914221</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5563,10 +5563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134095316</v>
+        <v>134095280</v>
       </c>
       <c r="B47" t="n">
-        <v>79390</v>
+        <v>92228</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5574,21 +5574,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589589</v>
+        <v>589373</v>
       </c>
       <c r="R47" t="n">
-        <v>6914177</v>
+        <v>6914203</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5670,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134095318</v>
+        <v>134095326</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>79977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,42 +5681,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589619</v>
+        <v>589658</v>
       </c>
       <c r="R48" t="n">
-        <v>6914175</v>
+        <v>6914134</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5748,7 +5740,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5758,12 +5750,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5790,10 +5777,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134095264</v>
+        <v>134095250</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>79390</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5801,42 +5788,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589558</v>
+        <v>589517</v>
       </c>
       <c r="R49" t="n">
-        <v>6914160</v>
+        <v>6914061</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5868,7 +5847,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5878,12 +5857,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5910,10 +5884,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134095355</v>
+        <v>134095318</v>
       </c>
       <c r="B50" t="n">
-        <v>79390</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5921,34 +5895,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589591</v>
+        <v>589619</v>
       </c>
       <c r="R50" t="n">
-        <v>6914124</v>
+        <v>6914175</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5980,7 +5962,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5990,7 +5972,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6017,10 +6004,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134095273</v>
+        <v>134095264</v>
       </c>
       <c r="B51" t="n">
-        <v>79390</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6028,34 +6015,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lobölebodarna, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589415</v>
+        <v>589558</v>
       </c>
       <c r="R51" t="n">
-        <v>6914094</v>
+        <v>6914160</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6087,7 +6082,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6097,7 +6092,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6124,10 +6124,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134095326</v>
+        <v>134095355</v>
       </c>
       <c r="B52" t="n">
-        <v>79977</v>
+        <v>79390</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6135,21 +6135,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589658</v>
+        <v>589591</v>
       </c>
       <c r="R52" t="n">
-        <v>6914134</v>
+        <v>6914124</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6231,7 +6231,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134095250</v>
+        <v>134095273</v>
       </c>
       <c r="B53" t="n">
         <v>79390</v>
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589517</v>
+        <v>589415</v>
       </c>
       <c r="R53" t="n">
-        <v>6914061</v>
+        <v>6914094</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6338,32 +6338,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134095296</v>
+        <v>134095272</v>
       </c>
       <c r="B54" t="n">
-        <v>80423</v>
+        <v>79390</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6373,10 +6373,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589458</v>
+        <v>589461</v>
       </c>
       <c r="R54" t="n">
-        <v>6914224</v>
+        <v>6914134</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6445,32 +6445,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134095277</v>
+        <v>134095296</v>
       </c>
       <c r="B55" t="n">
-        <v>80336</v>
+        <v>80423</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>392</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589390</v>
+        <v>589458</v>
       </c>
       <c r="R55" t="n">
-        <v>6914193</v>
+        <v>6914224</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6552,32 +6552,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134095353</v>
+        <v>134095277</v>
       </c>
       <c r="B56" t="n">
-        <v>79358</v>
+        <v>80336</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589598</v>
+        <v>589390</v>
       </c>
       <c r="R56" t="n">
-        <v>6914117</v>
+        <v>6914193</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6659,10 +6659,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134095272</v>
+        <v>134095353</v>
       </c>
       <c r="B57" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6670,21 +6670,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6694,10 +6694,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589461</v>
+        <v>589598</v>
       </c>
       <c r="R57" t="n">
-        <v>6914134</v>
+        <v>6914117</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
